--- a/7 Future comparisons/Bonaire/output/yearly_surface_area_growth_param_0.5.xlsx
+++ b/7 Future comparisons/Bonaire/output/yearly_surface_area_growth_param_0.5.xlsx
@@ -790,10 +790,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>11.49332037361741</v>
+        <v>11.75642875835555</v>
       </c>
       <c r="D2" t="n">
-        <v>94.83388298712914</v>
+        <v>95.47987297652355</v>
       </c>
     </row>
     <row r="3">
@@ -801,13 +801,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.330268139254428</v>
+        <v>2.493639168786899</v>
       </c>
       <c r="C3" t="n">
-        <v>14.72621556370216</v>
+        <v>18.02979658849267</v>
       </c>
       <c r="D3" t="n">
-        <v>301.7745180699058</v>
+        <v>277.2700953719054</v>
       </c>
     </row>
     <row r="4">
@@ -815,13 +815,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.38885420633975</v>
+        <v>14.67712817848981</v>
       </c>
       <c r="C4" t="n">
-        <v>70.20772357380216</v>
+        <v>71.98174167537614</v>
       </c>
       <c r="D4" t="n">
-        <v>295.724988716337</v>
+        <v>269.4975987973834</v>
       </c>
     </row>
     <row r="5">
@@ -829,13 +829,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.69600236904876</v>
+        <v>20.02765316663493</v>
       </c>
       <c r="C5" t="n">
-        <v>99.96645998493149</v>
+        <v>92.62789589568656</v>
       </c>
       <c r="D5" t="n">
-        <v>165.768099862074</v>
+        <v>162.6755945936965</v>
       </c>
     </row>
     <row r="6">
@@ -843,13 +843,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.901907345033331</v>
+        <v>9.861655689159212</v>
       </c>
       <c r="C6" t="n">
-        <v>48.90576188705487</v>
+        <v>44.80009298789471</v>
       </c>
       <c r="D6" t="n">
-        <v>118.0178550229176</v>
+        <v>117.9373517111694</v>
       </c>
     </row>
     <row r="7">
@@ -857,13 +857,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3.772856427420492</v>
+        <v>3.712969817461437</v>
       </c>
       <c r="C7" t="n">
-        <v>12.45641487148353</v>
+        <v>11.91743538185203</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4433116317549</v>
+        <v>103.6038352291659</v>
       </c>
     </row>
     <row r="8">
@@ -871,13 +871,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.087596529856218</v>
+        <v>2.670353755551324</v>
       </c>
       <c r="C8" t="n">
-        <v>7.760715602071035</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="D8" t="n">
-        <v>130.0128484734051</v>
+        <v>119.0810877866169</v>
       </c>
     </row>
     <row r="9">
@@ -885,13 +885,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.217187226816797</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>8.320311793491715</v>
+        <v>7.321874378272709</v>
       </c>
       <c r="D9" t="n">
-        <v>149.0999873393716</v>
+        <v>139.3374881683413</v>
       </c>
     </row>
     <row r="10">
@@ -899,13 +899,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="D10" t="n">
-        <v>157.7275861642926</v>
+        <v>157.3005259129452</v>
       </c>
     </row>
     <row r="11">
@@ -913,13 +913,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.954659679155399</v>
+        <v>2.310052348092745</v>
       </c>
       <c r="C11" t="n">
-        <v>8.707120388964958</v>
+        <v>9.062513057902304</v>
       </c>
       <c r="D11" t="n">
-        <v>166.1460727282089</v>
+        <v>173.2539261069558</v>
       </c>
     </row>
     <row r="12">
@@ -927,13 +927,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.952696183746906</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>7.810784734987623</v>
+        <v>8.244717220264713</v>
       </c>
       <c r="D12" t="n">
-        <v>160.1210870672463</v>
+        <v>183.5534412722091</v>
       </c>
     </row>
     <row r="13">
@@ -941,13 +941,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>8.585383673638358</v>
+        <v>7.024404823885929</v>
       </c>
       <c r="D13" t="n">
-        <v>118.1140662979338</v>
+        <v>177.431262588526</v>
       </c>
     </row>
     <row r="14">
@@ -955,13 +955,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.458296251434013</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>9.525897974306801</v>
+        <v>6.760314691443536</v>
       </c>
       <c r="D14" t="n">
-        <v>96.79541490021428</v>
+        <v>143.8103307088898</v>
       </c>
     </row>
     <row r="15">
@@ -969,13 +969,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>11.46681318560274</v>
+        <v>7.883434065101886</v>
       </c>
       <c r="D15" t="n">
-        <v>66.65085164131595</v>
+        <v>131.1516758103314</v>
       </c>
     </row>
     <row r="16">
@@ -983,13 +983,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>11.15952615417349</v>
+        <v>9.506263020221864</v>
       </c>
       <c r="D16" t="n">
-        <v>31.82531532856885</v>
+        <v>114.4884720261503</v>
       </c>
     </row>
     <row r="17">
@@ -997,13 +997,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>4.722206457427158</v>
+        <v>10.86107485208246</v>
       </c>
       <c r="D17" t="n">
-        <v>7.555530331883453</v>
+        <v>94.91634979428588</v>
       </c>
     </row>
     <row r="18">
@@ -1011,13 +1011,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>63.67124735892688</v>
       </c>
     </row>
     <row r="19">
@@ -1028,10 +1028,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>22.8688310227252</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>20.46158565191202</v>
       </c>
     </row>
     <row r="20">
@@ -1101,10 +1101,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>15.86504290062845</v>
+        <v>16.33726354637117</v>
       </c>
       <c r="D2" t="n">
-        <v>83.45346359950013</v>
+        <v>84.97909953189966</v>
       </c>
     </row>
     <row r="3">
@@ -1112,13 +1112,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5301437602932776</v>
+        <v>1.060287520586555</v>
       </c>
       <c r="C3" t="n">
-        <v>31.78408192499048</v>
+        <v>32.46148784092079</v>
       </c>
       <c r="D3" t="n">
-        <v>306.0451205833794</v>
+        <v>282.38009217251</v>
       </c>
     </row>
     <row r="4">
@@ -1126,13 +1126,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>6.075054793879263</v>
+        <v>9.138107631129312</v>
       </c>
       <c r="C4" t="n">
-        <v>52.86318688287376</v>
+        <v>57.49605429921445</v>
       </c>
       <c r="D4" t="n">
-        <v>355.27584096054</v>
+        <v>321.9651413554457</v>
       </c>
     </row>
     <row r="5">
@@ -1140,13 +1140,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.32784697995621</v>
+        <v>21.40209995258047</v>
       </c>
       <c r="C5" t="n">
-        <v>116.9506952684013</v>
+        <v>111.7719761284994</v>
       </c>
       <c r="D5" t="n">
-        <v>208.7195619228719</v>
+        <v>200.5219685924111</v>
       </c>
     </row>
     <row r="6">
@@ -1154,13 +1154,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.54972196111598</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="C6" t="n">
-        <v>100.7901463087946</v>
+        <v>94.26937805718724</v>
       </c>
       <c r="D6" t="n">
-        <v>132.4681994817264</v>
+        <v>133.8367557814464</v>
       </c>
     </row>
     <row r="7">
@@ -1168,13 +1168,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.665486074759095</v>
+        <v>8.204465564390594</v>
       </c>
       <c r="C7" t="n">
-        <v>38.68675003354981</v>
+        <v>37.4890178343687</v>
       </c>
       <c r="D7" t="n">
-        <v>119.1743538185203</v>
+        <v>111.6885275736384</v>
       </c>
     </row>
     <row r="8">
@@ -1182,13 +1182,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.67173641388307</v>
+        <v>3.504839304161113</v>
       </c>
       <c r="C8" t="n">
-        <v>11.68279768053704</v>
+        <v>11.01520924164921</v>
       </c>
       <c r="D8" t="n">
-        <v>132.9335478935394</v>
+        <v>119.6652276706437</v>
       </c>
     </row>
     <row r="9">
@@ -1196,13 +1196,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.328124717396686</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>9.096874227550941</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="D9" t="n">
-        <v>153.5374869625671</v>
+        <v>138.6718632248619</v>
       </c>
     </row>
     <row r="10">
@@ -1210,13 +1210,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>9.680032363873552</v>
+        <v>8.541205026947251</v>
       </c>
       <c r="D10" t="n">
-        <v>157.8699395814083</v>
+        <v>158.1546464156399</v>
       </c>
     </row>
     <row r="11">
@@ -1224,13 +1224,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.954659679155399</v>
+        <v>2.487748682561417</v>
       </c>
       <c r="C11" t="n">
         <v>9.417905726839649</v>
       </c>
       <c r="D11" t="n">
-        <v>166.1460727282089</v>
+        <v>172.1877481001438</v>
       </c>
     </row>
     <row r="12">
@@ -1238,13 +1238,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.952696183746906</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>8.678649705541803</v>
+        <v>9.112582190818895</v>
       </c>
       <c r="D12" t="n">
-        <v>154.2629985160056</v>
+        <v>184.6382724854019</v>
       </c>
     </row>
     <row r="13">
@@ -1252,13 +1252,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>8.845546815263763</v>
+        <v>8.065057390387548</v>
       </c>
       <c r="D13" t="n">
-        <v>114.4717823151781</v>
+        <v>177.9515888717769</v>
       </c>
     </row>
     <row r="14">
@@ -1266,13 +1266,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>9.833185005736054</v>
+        <v>7.067601722872788</v>
       </c>
       <c r="D14" t="n">
-        <v>90.64967427162925</v>
+        <v>148.7269232117578</v>
       </c>
     </row>
     <row r="15">
@@ -1280,13 +1280,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.791689560250429</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="D15" t="n">
-        <v>58.76741757621406</v>
+        <v>132.9433653705818</v>
       </c>
     </row>
     <row r="16">
@@ -1294,13 +1294,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>10.33289458719768</v>
+        <v>9.092947236733956</v>
       </c>
       <c r="D16" t="n">
-        <v>25.21226279276234</v>
+        <v>114.9017878096382</v>
       </c>
     </row>
     <row r="17">
@@ -1308,13 +1308,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>3.777765165941727</v>
+        <v>10.38885420633975</v>
       </c>
       <c r="D17" t="n">
-        <v>5.194427103169874</v>
+        <v>96.33301173151402</v>
       </c>
     </row>
     <row r="18">
@@ -1322,13 +1322,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>65.81145735418494</v>
       </c>
     </row>
     <row r="19">
@@ -1336,13 +1336,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>22.26701968002191</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>6.724971774090649</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
     </row>
     <row r="21">
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>12.22374066557704</v>
+        <v>12.93452600345173</v>
       </c>
       <c r="D2" t="n">
-        <v>148.4520338545687</v>
+        <v>151.4669810543107</v>
       </c>
     </row>
     <row r="3">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2208932334555324</v>
+        <v>0.4663301595172349</v>
       </c>
       <c r="C3" t="n">
-        <v>48.2774433563369</v>
+        <v>47.5705850092792</v>
       </c>
       <c r="D3" t="n">
-        <v>302.3390229998477</v>
+        <v>280.028806420839</v>
       </c>
     </row>
     <row r="4">
@@ -1437,13 +1437,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3.280019079888593</v>
+        <v>5.245477983790708</v>
       </c>
       <c r="C4" t="n">
-        <v>67.13190801639689</v>
+        <v>68.14016290865837</v>
       </c>
       <c r="D4" t="n">
-        <v>399.4348526975616</v>
+        <v>360.5213189443307</v>
       </c>
     </row>
     <row r="5">
@@ -1451,13 +1451,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.71992416684918</v>
+        <v>17.69600236904876</v>
       </c>
       <c r="C5" t="n">
-        <v>108.4340339340602</v>
+        <v>106.7405191442345</v>
       </c>
       <c r="D5" t="n">
-        <v>259.034131765521</v>
+        <v>244.7251589761237</v>
       </c>
     </row>
     <row r="6">
@@ -1465,13 +1465,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.41388092503143</v>
+        <v>24.75476836258333</v>
       </c>
       <c r="C6" t="n">
-        <v>141.9675902680185</v>
+        <v>132.5889544493488</v>
       </c>
       <c r="D6" t="n">
-        <v>152.2720141717931</v>
+        <v>156.4581863827015</v>
       </c>
     </row>
     <row r="7">
@@ -1479,13 +1479,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.95358012045992</v>
+        <v>16.16938468894497</v>
       </c>
       <c r="C7" t="n">
-        <v>85.21864597173588</v>
+        <v>83.42204767296421</v>
       </c>
       <c r="D7" t="n">
-        <v>125.2229014243849</v>
+        <v>119.7133333081518</v>
       </c>
     </row>
     <row r="8">
@@ -1493,13 +1493,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>27.62147165898401</v>
+        <v>29.04009709162065</v>
       </c>
       <c r="D8" t="n">
-        <v>136.1045929782565</v>
+        <v>121.5010958775852</v>
       </c>
     </row>
     <row r="9">
@@ -1507,13 +1507,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.549999698556465</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>11.31562403914873</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="D9" t="n">
-        <v>156.5327992082241</v>
+        <v>138.2281132625424</v>
       </c>
     </row>
     <row r="10">
@@ -1524,10 +1524,10 @@
         <v>2.989421759431538</v>
       </c>
       <c r="C10" t="n">
-        <v>10.53415286656828</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="D10" t="n">
-        <v>160.0052408381452</v>
+        <v>158.8664135012189</v>
       </c>
     </row>
     <row r="11">
@@ -1535,13 +1535,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.132356013624072</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>10.12869106471434</v>
+        <v>9.595602061308321</v>
       </c>
       <c r="D11" t="n">
-        <v>164.5468057179908</v>
+        <v>171.2992664278004</v>
       </c>
     </row>
     <row r="12">
@@ -1549,13 +1549,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.952696183746906</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>9.329548433457438</v>
+        <v>9.980447161373073</v>
       </c>
       <c r="D12" t="n">
-        <v>149.272774935319</v>
+        <v>183.5534412722091</v>
       </c>
     </row>
     <row r="13">
@@ -1563,13 +1563,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
         <v>9.105709956889166</v>
       </c>
       <c r="D13" t="n">
-        <v>111.0896614740478</v>
+        <v>180.8133834296563</v>
       </c>
     </row>
     <row r="14">
@@ -1577,13 +1577,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>10.14047203716531</v>
+        <v>7.682175785731292</v>
       </c>
       <c r="D14" t="n">
-        <v>84.81122067447346</v>
+        <v>151.4925064946211</v>
       </c>
     </row>
     <row r="15">
@@ -1591,13 +1591,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="D15" t="n">
-        <v>51.24232142316227</v>
+        <v>134.0183791067321</v>
       </c>
     </row>
     <row r="16">
@@ -1605,13 +1605,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>9.919578803709772</v>
+        <v>8.679631453246051</v>
       </c>
       <c r="D16" t="n">
-        <v>19.83915760741954</v>
+        <v>117.3816825105656</v>
       </c>
     </row>
     <row r="17">
@@ -1619,13 +1619,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>2.833323874456295</v>
+        <v>9.916633560597033</v>
       </c>
       <c r="D17" t="n">
-        <v>3.305544520199011</v>
+        <v>97.27745302299945</v>
       </c>
     </row>
     <row r="18">
@@ -1633,13 +1633,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>2.675262494072558</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>68.48671984825749</v>
       </c>
     </row>
     <row r="19">
@@ -1647,13 +1647,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>25.87788773624167</v>
       </c>
     </row>
     <row r="20">
@@ -1664,10 +1664,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>12.10494919336317</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>2.017491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -1678,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.063234825386688</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -1723,10 +1723,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>15.66869335977909</v>
+        <v>16.09280836801372</v>
       </c>
       <c r="D2" t="n">
-        <v>139.6064870393049</v>
+        <v>143.0750016784089</v>
       </c>
     </row>
     <row r="3">
@@ -1734,13 +1734,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.09326603190344698</v>
+        <v>0.2159844949342983</v>
       </c>
       <c r="C3" t="n">
-        <v>48.08109381548754</v>
+        <v>48.39525308084652</v>
       </c>
       <c r="D3" t="n">
-        <v>332.6063047217769</v>
+        <v>309.2701617918302</v>
       </c>
     </row>
     <row r="4">
@@ -1748,13 +1748,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.761255381418778</v>
+        <v>2.96095107600838</v>
       </c>
       <c r="C4" t="n">
-        <v>93.84428130124836</v>
+        <v>90.05375341515142</v>
       </c>
       <c r="D4" t="n">
-        <v>431.8266364514808</v>
+        <v>388.4333879237718</v>
       </c>
     </row>
     <row r="5">
@@ -1762,13 +1762,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.891108120286615</v>
+        <v>13.08178815908875</v>
       </c>
       <c r="C5" t="n">
-        <v>116.3371029532471</v>
+        <v>113.735471536993</v>
       </c>
       <c r="D5" t="n">
-        <v>307.3852061996764</v>
+        <v>286.5966985622501</v>
       </c>
     </row>
     <row r="6">
@@ -1776,13 +1776,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.97111271041612</v>
+        <v>24.79502001845745</v>
       </c>
       <c r="C6" t="n">
-        <v>158.2695108970368</v>
+        <v>146.3147691024234</v>
       </c>
       <c r="D6" t="n">
-        <v>175.4569679552857</v>
+        <v>181.1324514335365</v>
       </c>
     </row>
     <row r="7">
@@ -1790,13 +1790,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.52303484665207</v>
+        <v>22.93657161431823</v>
       </c>
       <c r="C7" t="n">
-        <v>134.1460063082842</v>
+        <v>130.4929231007818</v>
       </c>
       <c r="D7" t="n">
-        <v>132.1098615696763</v>
+        <v>131.750541909922</v>
       </c>
     </row>
     <row r="8">
@@ -1804,13 +1804,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="C8" t="n">
-        <v>60.24985660962675</v>
+        <v>64.58918146239766</v>
       </c>
       <c r="D8" t="n">
-        <v>137.8570126303371</v>
+        <v>123.9211039685536</v>
       </c>
     </row>
     <row r="9">
@@ -1818,13 +1818,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>19.41406085148067</v>
+        <v>21.63281066307846</v>
       </c>
       <c r="D9" t="n">
-        <v>161.0812363219996</v>
+        <v>137.8953007908027</v>
       </c>
     </row>
     <row r="10">
@@ -1832,13 +1832,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.131775176547325</v>
+        <v>3.274128593663113</v>
       </c>
       <c r="C10" t="n">
-        <v>11.81533362061037</v>
+        <v>10.67650628368406</v>
       </c>
       <c r="D10" t="n">
-        <v>160.0052408381452</v>
+        <v>157.5852327471768</v>
       </c>
     </row>
     <row r="11">
@@ -1846,13 +1846,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.310052348092745</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>11.0171727370577</v>
+        <v>9.950994730245668</v>
       </c>
       <c r="D11" t="n">
-        <v>162.7698423733041</v>
+        <v>170.7661774243944</v>
       </c>
     </row>
     <row r="12">
@@ -1860,13 +1860,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.952696183746906</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>9.980447161373073</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
-        <v>144.499517597271</v>
+        <v>184.4213062427633</v>
       </c>
     </row>
     <row r="13">
@@ -1874,13 +1874,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>107.4473774912922</v>
+        <v>180.8133834296563</v>
       </c>
     </row>
     <row r="14">
@@ -1891,10 +1891,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>10.44775906859456</v>
+        <v>8.604036880019047</v>
       </c>
       <c r="D14" t="n">
-        <v>78.66548004588843</v>
+        <v>154.2580897774843</v>
       </c>
     </row>
     <row r="15">
@@ -1902,13 +1902,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>7.883434065101886</v>
       </c>
       <c r="D15" t="n">
-        <v>44.43390109421063</v>
+        <v>135.4517307549324</v>
       </c>
     </row>
     <row r="16">
@@ -1916,13 +1916,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>9.092947236733956</v>
+        <v>8.266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>119.4482614280052</v>
       </c>
     </row>
     <row r="17">
@@ -1930,13 +1930,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>2.361103228713579</v>
+        <v>9.444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>2.361103228713579</v>
+        <v>98.2218943144849</v>
       </c>
     </row>
     <row r="18">
@@ -1944,13 +1944,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>12.84125997154828</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>70.62692984351554</v>
       </c>
     </row>
     <row r="19">
@@ -1958,13 +1958,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>29.48875579246144</v>
       </c>
     </row>
     <row r="20">
@@ -1975,10 +1975,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>16.81242943522663</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -1989,7 +1989,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.772703000235396</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2034,10 +2034,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>16.80457545359265</v>
+        <v>17.06964733373929</v>
       </c>
       <c r="D2" t="n">
-        <v>198.1382851664998</v>
+        <v>200.2657324416026</v>
       </c>
     </row>
     <row r="3">
@@ -2045,13 +2045,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.03926990816987241</v>
+        <v>0.1030835089459151</v>
       </c>
       <c r="C3" t="n">
-        <v>54.37900533823083</v>
+        <v>53.98139751801087</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9951999858457</v>
+        <v>332.9155552486146</v>
       </c>
     </row>
     <row r="4">
@@ -2059,13 +2059,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9572040116406401</v>
+        <v>1.684679060487527</v>
       </c>
       <c r="C4" t="n">
-        <v>106.5559505758361</v>
+        <v>101.7316423571672</v>
       </c>
       <c r="D4" t="n">
-        <v>472.718391828769</v>
+        <v>416.77938938849</v>
       </c>
     </row>
     <row r="5">
@@ -2073,13 +2073,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.774059159302993</v>
+        <v>9.22842841992002</v>
       </c>
       <c r="C5" t="n">
-        <v>141.4943878745716</v>
+        <v>132.5604837659256</v>
       </c>
       <c r="D5" t="n">
-        <v>351.1956975016903</v>
+        <v>323.7313054753858</v>
       </c>
     </row>
     <row r="6">
@@ -2087,13 +2087,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.43525839034661</v>
+        <v>21.65539086027615</v>
       </c>
       <c r="C6" t="n">
-        <v>170.9487824973844</v>
+        <v>159.4368089173863</v>
       </c>
       <c r="D6" t="n">
-        <v>198.6016700829043</v>
+        <v>207.5777893428329</v>
       </c>
     </row>
     <row r="7">
@@ -2101,13 +2101,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.51736534460484</v>
+        <v>26.52976821186155</v>
       </c>
       <c r="C7" t="n">
-        <v>173.4316224414245</v>
+        <v>163.3107853583442</v>
       </c>
       <c r="D7" t="n">
-        <v>142.1708120427976</v>
+        <v>143.9075237316102</v>
       </c>
     </row>
     <row r="8">
@@ -2115,13 +2115,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.35315143608837</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="C8" t="n">
-        <v>101.7237883755332</v>
+        <v>108.0658785449676</v>
       </c>
       <c r="D8" t="n">
-        <v>139.6094322824177</v>
+        <v>127.8431860470196</v>
       </c>
     </row>
     <row r="9">
@@ -2129,13 +2129,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>8.542186774651494</v>
       </c>
       <c r="C9" t="n">
-        <v>37.60780930658255</v>
+        <v>45.92812110007426</v>
       </c>
       <c r="D9" t="n">
-        <v>165.0749859828756</v>
+        <v>139.3374881683413</v>
       </c>
     </row>
     <row r="10">
@@ -2143,13 +2143,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.4164820107789</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>15.37416904850505</v>
+        <v>16.79770321966293</v>
       </c>
       <c r="D10" t="n">
-        <v>158.4393532498715</v>
+        <v>156.3040519931347</v>
       </c>
     </row>
     <row r="11">
@@ -2157,13 +2157,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.310052348092745</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>11.90565440940107</v>
+        <v>10.83947640258903</v>
       </c>
       <c r="D11" t="n">
-        <v>161.8813607009608</v>
+        <v>169.877695752051</v>
       </c>
     </row>
     <row r="12">
@@ -2171,13 +2171,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.952696183746906</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
         <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
-        <v>139.2923277739459</v>
+        <v>182.9025425442935</v>
       </c>
     </row>
     <row r="13">
@@ -2185,13 +2185,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>10.40652566501619</v>
       </c>
       <c r="D13" t="n">
-        <v>102.2441146587841</v>
+        <v>181.0735465712817</v>
       </c>
     </row>
     <row r="14">
@@ -2199,13 +2199,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.229148125717007</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>9.525897974306801</v>
       </c>
       <c r="D14" t="n">
-        <v>72.5197394173034</v>
+        <v>158.2528211860646</v>
       </c>
     </row>
     <row r="15">
@@ -2213,13 +2213,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="D15" t="n">
-        <v>37.9838186773091</v>
+        <v>136.5267444910827</v>
       </c>
     </row>
     <row r="16">
@@ -2227,13 +2227,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
         <v>8.266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>11.98615772114931</v>
+        <v>120.274892994981</v>
       </c>
     </row>
     <row r="17">
@@ -2241,13 +2241,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>1.888882582970863</v>
+        <v>8.9721922691116</v>
       </c>
       <c r="D17" t="n">
-        <v>1.416661937228147</v>
+        <v>99.16633560597033</v>
       </c>
     </row>
     <row r="18">
@@ -2255,13 +2255,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>11.77115497391926</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>72.76713983877359</v>
       </c>
     </row>
     <row r="19">
@@ -2269,13 +2269,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>33.09962384868121</v>
       </c>
     </row>
     <row r="20">
@@ -2286,10 +2286,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>6.052474596681584</v>
       </c>
     </row>
     <row r="21">
@@ -2300,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>2.484030729682204</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2345,10 +2345,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>32.48406803811847</v>
+        <v>31.50428382928014</v>
       </c>
       <c r="D2" t="n">
-        <v>154.1982031675253</v>
+        <v>155.4862561554971</v>
       </c>
     </row>
     <row r="3">
@@ -2356,13 +2356,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01472621556370216</v>
+        <v>0.05399612373357457</v>
       </c>
       <c r="C3" t="n">
-        <v>59.17975161199774</v>
+        <v>58.07528544472007</v>
       </c>
       <c r="D3" t="n">
-        <v>384.5063971067846</v>
+        <v>372.5585275461008</v>
       </c>
     </row>
     <row r="4">
@@ -2370,13 +2370,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5232715263635499</v>
+        <v>0.9699667317958486</v>
       </c>
       <c r="C4" t="n">
-        <v>118.3742294395592</v>
+        <v>111.7503776790059</v>
       </c>
       <c r="D4" t="n">
-        <v>508.5050591439737</v>
+        <v>451.4939882106572</v>
       </c>
     </row>
     <row r="5">
@@ -2384,13 +2384,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.66330159517235</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C5" t="n">
-        <v>164.2463909204914</v>
+        <v>151.5327581504952</v>
       </c>
       <c r="D5" t="n">
-        <v>388.6984598039185</v>
+        <v>356.6443972602601</v>
       </c>
     </row>
     <row r="6">
@@ -2398,13 +2398,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.17487426454295</v>
+        <v>17.95223851985718</v>
       </c>
       <c r="C6" t="n">
-        <v>192.9664382605276</v>
+        <v>177.1877891578729</v>
       </c>
       <c r="D6" t="n">
-        <v>227.1803457535289</v>
+        <v>234.0231272521292</v>
       </c>
     </row>
     <row r="7">
@@ -2412,13 +2412,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.05634483423634</v>
+        <v>26.35010838198439</v>
       </c>
       <c r="C7" t="n">
-        <v>203.6743604707475</v>
+        <v>186.0676971427852</v>
       </c>
       <c r="D7" t="n">
-        <v>151.0939169266968</v>
+        <v>157.1424645325614</v>
       </c>
     </row>
     <row r="8">
@@ -2426,13 +2426,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.27523351455438</v>
+        <v>23.36559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>143.7818600254666</v>
+        <v>149.1225675365692</v>
       </c>
       <c r="D8" t="n">
-        <v>144.3659999094935</v>
+        <v>132.3494080095125</v>
       </c>
     </row>
     <row r="9">
@@ -2440,13 +2440,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>13.09062388842696</v>
       </c>
       <c r="C9" t="n">
-        <v>64.12186955517615</v>
+        <v>78.4328058399819</v>
       </c>
       <c r="D9" t="n">
-        <v>165.5187359451952</v>
+        <v>140.8906130364597</v>
       </c>
     </row>
     <row r="10">
@@ -2454,13 +2454,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.128249096357838</v>
+        <v>5.836490101747287</v>
       </c>
       <c r="C10" t="n">
-        <v>23.06125357275758</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>158.1546464156399</v>
+        <v>155.0228712390926</v>
       </c>
     </row>
     <row r="11">
@@ -2468,13 +2468,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.487748682561417</v>
+        <v>3.37623035490478</v>
       </c>
       <c r="C11" t="n">
-        <v>13.32722508515045</v>
+        <v>13.86031408855647</v>
       </c>
       <c r="D11" t="n">
-        <v>159.038219349462</v>
+        <v>168.6338214107703</v>
       </c>
     </row>
     <row r="12">
@@ -2482,13 +2482,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.952696183746906</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
         <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>134.0851379506209</v>
+        <v>181.3837788458237</v>
       </c>
     </row>
     <row r="13">
@@ -2499,10 +2499,10 @@
         <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>10.40652566501619</v>
+        <v>10.926851948267</v>
       </c>
       <c r="D13" t="n">
-        <v>97.56117810952679</v>
+        <v>180.8133834296563</v>
       </c>
     </row>
     <row r="14">
@@ -2510,13 +2510,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.14047203716531</v>
       </c>
       <c r="D14" t="n">
-        <v>65.75942472585986</v>
+        <v>159.7892563432109</v>
       </c>
     </row>
     <row r="15">
@@ -2524,13 +2524,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>8.958447801252145</v>
       </c>
       <c r="D15" t="n">
-        <v>32.25041208450772</v>
+        <v>139.0351098754333</v>
       </c>
     </row>
     <row r="16">
@@ -2538,13 +2538,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>7.439684102782329</v>
+        <v>8.266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>120.6882087784689</v>
       </c>
     </row>
     <row r="17">
@@ -2552,13 +2552,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>1.416661937228147</v>
+        <v>8.9721922691116</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9444412914854317</v>
+        <v>100.1107768974558</v>
       </c>
     </row>
     <row r="18">
@@ -2566,13 +2566,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>10.70104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>74.37229733521713</v>
       </c>
     </row>
     <row r="19">
@@ -2580,13 +2580,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>15.04528356758237</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>36.10868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2597,10 +2597,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>24.20989838672634</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>8.06996612890878</v>
       </c>
     </row>
     <row r="21">
@@ -2611,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>2.842585855541444</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2656,10 +2656,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>22.79225470179395</v>
+        <v>23.16531882940774</v>
       </c>
       <c r="D2" t="n">
-        <v>195.1969690445763</v>
+        <v>195.155735640998</v>
       </c>
     </row>
     <row r="3">
@@ -2667,13 +2667,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.004908738521234052</v>
+        <v>0.02945243112740431</v>
       </c>
       <c r="C3" t="n">
-        <v>87.36081946240243</v>
+        <v>80.34132337703772</v>
       </c>
       <c r="D3" t="n">
-        <v>400.057280742054</v>
+        <v>384.0842455939584</v>
       </c>
     </row>
     <row r="4">
@@ -2681,13 +2681,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2935425635697963</v>
+        <v>0.5743224069843841</v>
       </c>
       <c r="C4" t="n">
-        <v>130.6774916691802</v>
+        <v>120.4545528248582</v>
       </c>
       <c r="D4" t="n">
-        <v>540.1948932893565</v>
+        <v>483.068957874643</v>
       </c>
     </row>
     <row r="5">
@@ -2695,13 +2695,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.190680038802134</v>
+        <v>4.442408361716818</v>
       </c>
       <c r="C5" t="n">
-        <v>184.9121800948868</v>
+        <v>168.1979254300848</v>
       </c>
       <c r="D5" t="n">
-        <v>431.5026597090794</v>
+        <v>394.9080140332796</v>
       </c>
     </row>
     <row r="6">
@@ -2709,13 +2709,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.27675504160637</v>
+        <v>14.20883452356409</v>
       </c>
       <c r="C6" t="n">
-        <v>218.3652331170968</v>
+        <v>195.7035508599677</v>
       </c>
       <c r="D6" t="n">
-        <v>254.3099618126853</v>
+        <v>259.2206638293279</v>
       </c>
     </row>
     <row r="7">
@@ -2723,13 +2723,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.97838585497334</v>
+        <v>24.67328330313084</v>
       </c>
       <c r="C7" t="n">
-        <v>230.9227680021177</v>
+        <v>209.9624545164483</v>
       </c>
       <c r="D7" t="n">
-        <v>160.1367950305142</v>
+        <v>170.7966116032261</v>
       </c>
     </row>
     <row r="8">
@@ -2737,13 +2737,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.69524160552276</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="C8" t="n">
-        <v>183.5033721392925</v>
+        <v>181.750952487212</v>
       </c>
       <c r="D8" t="n">
-        <v>147.4535964393497</v>
+        <v>137.2728727463102</v>
       </c>
     </row>
     <row r="9">
@@ -2751,13 +2751,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.42656152972862</v>
+        <v>17.30624853046277</v>
       </c>
       <c r="C9" t="n">
-        <v>96.40467931392402</v>
+        <v>116.3734276183041</v>
       </c>
       <c r="D9" t="n">
-        <v>167.2937357944734</v>
+        <v>141.1124880176195</v>
       </c>
     </row>
     <row r="10">
@@ -2765,13 +2765,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>8.683558444063038</v>
       </c>
       <c r="C10" t="n">
-        <v>35.58835427894688</v>
+        <v>52.10135066437823</v>
       </c>
       <c r="D10" t="n">
-        <v>157.442879330061</v>
+        <v>154.1687507363979</v>
       </c>
     </row>
     <row r="11">
@@ -2779,13 +2779,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.665445017030089</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>21.50125647070939</v>
       </c>
       <c r="D11" t="n">
-        <v>155.6619889945572</v>
+        <v>168.9892140797077</v>
       </c>
     </row>
     <row r="12">
@@ -2793,13 +2793,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.952696183746906</v>
+        <v>2.603594911662541</v>
       </c>
       <c r="C12" t="n">
-        <v>12.15010958775853</v>
+        <v>12.80100831567416</v>
       </c>
       <c r="D12" t="n">
-        <v>128.4440156420187</v>
+        <v>179.6480489047153</v>
       </c>
     </row>
     <row r="13">
@@ -2807,13 +2807,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>10.6666888066416</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>91.83758899376788</v>
+        <v>180.0328940047801</v>
       </c>
     </row>
     <row r="14">
@@ -2821,13 +2821,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6145740628585034</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>59.30639706584557</v>
+        <v>160.7111174374986</v>
       </c>
     </row>
     <row r="15">
@@ -2835,13 +2835,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>9.316785713302231</v>
       </c>
       <c r="D15" t="n">
-        <v>26.87534340375643</v>
+        <v>139.7517856995334</v>
       </c>
     </row>
     <row r="16">
@@ -2849,13 +2849,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>6.613052535806514</v>
+        <v>8.679631453246051</v>
       </c>
       <c r="D16" t="n">
-        <v>6.613052535806514</v>
+        <v>121.1015245619568</v>
       </c>
     </row>
     <row r="17">
@@ -2863,13 +2863,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9444412914854317</v>
+        <v>8.499971623368884</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>101.9996594804266</v>
       </c>
     </row>
     <row r="18">
@@ -2877,13 +2877,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>10.16599747747572</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>75.44240233284614</v>
       </c>
     </row>
     <row r="19">
@@ -2891,13 +2891,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>13.84166088217578</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>38.51592593301086</v>
       </c>
     </row>
     <row r="20">
@@ -2908,10 +2908,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>26.8998870963626</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>10.08745766113597</v>
       </c>
     </row>
     <row r="21">
@@ -2922,7 +2922,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>3.203039619096264</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2967,10 +2967,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>24.08914341910398</v>
+        <v>23.82603503436584</v>
       </c>
       <c r="D2" t="n">
-        <v>180.9704630623358</v>
+        <v>180.8516715901219</v>
       </c>
     </row>
     <row r="3">
@@ -2978,13 +2978,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.01472621556370216</v>
       </c>
       <c r="C3" t="n">
-        <v>86.5656038219625</v>
+        <v>82.09374302911829</v>
       </c>
       <c r="D3" t="n">
-        <v>427.5658514150496</v>
+        <v>405.7906873348554</v>
       </c>
     </row>
     <row r="4">
@@ -2992,13 +2992,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.165915362017711</v>
+        <v>0.3445934441906304</v>
       </c>
       <c r="C4" t="n">
-        <v>163.4649197479109</v>
+        <v>142.8020758166283</v>
       </c>
       <c r="D4" t="n">
-        <v>566.9583174548287</v>
+        <v>508.2880929013351</v>
       </c>
     </row>
     <row r="5">
@@ -3006,13 +3006,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2.208932334555324</v>
+        <v>3.117048960983624</v>
       </c>
       <c r="C5" t="n">
-        <v>204.4980467946106</v>
+        <v>182.5559856046944</v>
       </c>
       <c r="D5" t="n">
-        <v>469.1526841669446</v>
+        <v>425.244018094506</v>
       </c>
     </row>
     <row r="6">
@@ -3020,13 +3020,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.821404033285093</v>
+        <v>11.27046364475338</v>
       </c>
       <c r="C6" t="n">
-        <v>242.1539617387013</v>
+        <v>214.4205708414332</v>
       </c>
       <c r="D6" t="n">
-        <v>279.9905182603734</v>
+        <v>289.650915670162</v>
       </c>
     </row>
     <row r="7">
@@ -3034,13 +3034,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.00212772632452</v>
+        <v>21.79872602509618</v>
       </c>
       <c r="C7" t="n">
-        <v>262.0039185708675</v>
+        <v>232.4798198610532</v>
       </c>
       <c r="D7" t="n">
-        <v>168.580807034741</v>
+        <v>184.2112122340545</v>
       </c>
     </row>
     <row r="8">
@@ -3048,13 +3048,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.94696992843745</v>
+        <v>26.45319189093031</v>
       </c>
       <c r="C8" t="n">
-        <v>219.0524565100695</v>
+        <v>210.6241524691107</v>
       </c>
       <c r="D8" t="n">
-        <v>151.2922299629547</v>
+        <v>142.36323459283</v>
       </c>
     </row>
     <row r="9">
@@ -3062,13 +3062,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.86718632248619</v>
+        <v>20.52343575727956</v>
       </c>
       <c r="C9" t="n">
-        <v>129.0203015444115</v>
+        <v>151.9843620944487</v>
       </c>
       <c r="D9" t="n">
-        <v>166.6281108509941</v>
+        <v>141.4453004893592</v>
       </c>
     </row>
     <row r="10">
@@ -3076,13 +3076,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>11.67298020349457</v>
       </c>
       <c r="C10" t="n">
-        <v>52.67076433284138</v>
+        <v>78.57908624791472</v>
       </c>
       <c r="D10" t="n">
-        <v>155.0228712390926</v>
+        <v>153.1722768165874</v>
       </c>
     </row>
     <row r="11">
@@ -3090,13 +3090,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>152.1080623051838</v>
+        <v>167.3899470694896</v>
       </c>
     </row>
     <row r="12">
@@ -3104,13 +3104,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.952696183746906</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>13.0179745583127</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>123.0198595760551</v>
+        <v>178.1292852062455</v>
       </c>
     </row>
     <row r="13">
@@ -3118,13 +3118,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>12.22766765639403</v>
       </c>
       <c r="D13" t="n">
-        <v>86.63432616125979</v>
+        <v>180.8133834296563</v>
       </c>
     </row>
     <row r="14">
@@ -3132,13 +3132,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>52.54608237440203</v>
+        <v>161.0184044689279</v>
       </c>
     </row>
     <row r="15">
@@ -3146,13 +3146,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>10.0334615374024</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>140.1101236115835</v>
       </c>
     </row>
     <row r="16">
@@ -3160,13 +3160,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>5.7864209688307</v>
+        <v>8.679631453246051</v>
       </c>
       <c r="D16" t="n">
-        <v>4.959789401854886</v>
+        <v>121.1015245619568</v>
       </c>
     </row>
     <row r="17">
@@ -3174,13 +3174,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>8.499971623368884</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>101.9996594804266</v>
       </c>
     </row>
     <row r="18">
@@ -3188,13 +3188,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>9.63094497866121</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>76.51250733047517</v>
       </c>
     </row>
     <row r="19">
@@ -3205,10 +3205,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>12.63803819676919</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>40.92317130382404</v>
       </c>
     </row>
     <row r="20">
@@ -3219,10 +3219,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>28.91737862858979</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -3233,7 +3233,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>3.20876026613472</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -3278,10 +3278,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>24.29825568010855</v>
+        <v>23.60808704402305</v>
       </c>
       <c r="D2" t="n">
-        <v>197.2390042694097</v>
+        <v>195.1616261272234</v>
       </c>
     </row>
     <row r="3">
@@ -3289,13 +3289,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.004908738521234052</v>
       </c>
       <c r="C3" t="n">
-        <v>88.568369138626</v>
+        <v>84.54320355121408</v>
       </c>
       <c r="D3" t="n">
-        <v>442.7731233538327</v>
+        <v>416.2659353391689</v>
       </c>
     </row>
     <row r="4">
@@ -3303,13 +3303,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.08933904108645975</v>
+        <v>0.2169662426385451</v>
       </c>
       <c r="C4" t="n">
-        <v>180.1713204310789</v>
+        <v>156.7517289462712</v>
       </c>
       <c r="D4" t="n">
-        <v>591.5520791939156</v>
+        <v>529.946429004724</v>
       </c>
     </row>
     <row r="5">
@@ -3317,13 +3317,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.570796326794897</v>
+        <v>2.233476027161494</v>
       </c>
       <c r="C5" t="n">
-        <v>235.9385170231147</v>
+        <v>200.8655802888975</v>
       </c>
       <c r="D5" t="n">
-        <v>501.1331156327844</v>
+        <v>450.622196249286</v>
       </c>
     </row>
     <row r="6">
@@ -3331,13 +3331,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.768569583705012</v>
+        <v>8.815112636432113</v>
       </c>
       <c r="C6" t="n">
-        <v>268.9615645508647</v>
+        <v>234.626902090241</v>
       </c>
       <c r="D6" t="n">
-        <v>300.3176044768036</v>
+        <v>314.6874456238642</v>
       </c>
     </row>
     <row r="7">
@@ -3345,13 +3345,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.02586959767568</v>
+        <v>18.98405535702057</v>
       </c>
       <c r="C7" t="n">
-        <v>289.491872542074</v>
+        <v>251.5237618280328</v>
       </c>
       <c r="D7" t="n">
-        <v>178.222551238149</v>
+        <v>199.841617433368</v>
       </c>
     </row>
     <row r="8">
@@ -3359,13 +3359,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.1138670381594</v>
+        <v>25.36836067773758</v>
       </c>
       <c r="C8" t="n">
-        <v>254.0174009968197</v>
+        <v>239.4973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>156.5494889191964</v>
+        <v>148.4549790976814</v>
       </c>
     </row>
     <row r="9">
@@ -3373,13 +3373,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.53124868118453</v>
+        <v>22.74218556887735</v>
       </c>
       <c r="C9" t="n">
-        <v>161.9687362466387</v>
+        <v>182.7140469850781</v>
       </c>
       <c r="D9" t="n">
-        <v>164.2984235488164</v>
+        <v>143.6640503009569</v>
       </c>
     </row>
     <row r="10">
@@ -3387,13 +3387,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.975317438673588</v>
+        <v>14.23534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>72.45788931193584</v>
+        <v>108.4733038422301</v>
       </c>
       <c r="D10" t="n">
-        <v>153.7416904850505</v>
+        <v>152.0334494796611</v>
       </c>
     </row>
     <row r="11">
@@ -3401,13 +3401,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>49.22188464782232</v>
       </c>
       <c r="D11" t="n">
-        <v>147.8433502779357</v>
+        <v>165.6129837248029</v>
       </c>
     </row>
     <row r="12">
@@ -3415,13 +3415,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.735729941108361</v>
+        <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>14.31977201414398</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>117.1617710248143</v>
+        <v>176.1765890224986</v>
       </c>
     </row>
     <row r="13">
@@ -3429,13 +3429,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.040652566501619</v>
+        <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>80.39041076225007</v>
+        <v>179.2524045799039</v>
       </c>
     </row>
     <row r="14">
@@ -3443,13 +3443,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>46.400341745817</v>
+        <v>161.3256915003571</v>
       </c>
     </row>
     <row r="15">
@@ -3457,13 +3457,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>10.39179944945249</v>
       </c>
       <c r="D15" t="n">
-        <v>17.91689560250429</v>
+        <v>141.901813171834</v>
       </c>
     </row>
     <row r="16">
@@ -3471,13 +3471,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>4.959789401854886</v>
+        <v>9.092947236733956</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>120.6882087784689</v>
       </c>
     </row>
     <row r="17">
@@ -3485,13 +3485,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>8.499971623368884</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>101.9996594804266</v>
       </c>
     </row>
     <row r="18">
@@ -3502,10 +3502,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>77.04755982928968</v>
       </c>
     </row>
     <row r="19">
@@ -3516,10 +3516,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>12.03622685406589</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>42.72860533193393</v>
       </c>
     </row>
     <row r="20">
@@ -3530,10 +3530,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>30.93487016081699</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -3544,7 +3544,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>3.214888257255486</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -3589,10 +3589,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>29.63699969580271</v>
+        <v>27.78542352559323</v>
       </c>
       <c r="D2" t="n">
-        <v>165.6640346054238</v>
+        <v>162.7688606255999</v>
       </c>
     </row>
     <row r="3">
@@ -3603,10 +3603,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>89.76610133780711</v>
+        <v>84.74446183058467</v>
       </c>
       <c r="D3" t="n">
-        <v>454.1712142001382</v>
+        <v>434.0895649097697</v>
       </c>
     </row>
     <row r="4">
@@ -3614,13 +3614,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.05105088062083414</v>
+        <v>0.1276272015520853</v>
       </c>
       <c r="C4" t="n">
-        <v>191.3259378467312</v>
+        <v>168.3275161270454</v>
       </c>
       <c r="D4" t="n">
-        <v>622.2208957268817</v>
+        <v>545.861541038269</v>
       </c>
     </row>
     <row r="5">
@@ -3628,13 +3628,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.129009859883832</v>
+        <v>1.595340019401067</v>
       </c>
       <c r="C5" t="n">
-        <v>261.783025337412</v>
+        <v>217.9234466501858</v>
       </c>
       <c r="D5" t="n">
-        <v>522.5352155853649</v>
+        <v>470.797111571558</v>
       </c>
     </row>
     <row r="6">
@@ -3642,13 +3642,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>6.158503348740243</v>
+        <v>6.963536466222627</v>
       </c>
       <c r="C6" t="n">
-        <v>300.5993660679225</v>
+        <v>252.3376306748535</v>
       </c>
       <c r="D6" t="n">
-        <v>324.9113662158904</v>
+        <v>336.4635914517626</v>
       </c>
     </row>
     <row r="7">
@@ -3656,13 +3656,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.9897248590678</v>
+        <v>16.16938468894497</v>
       </c>
       <c r="C7" t="n">
-        <v>318.2374453224205</v>
+        <v>273.8015807328014</v>
       </c>
       <c r="D7" t="n">
-        <v>187.1456561220482</v>
+        <v>214.2144038235413</v>
       </c>
     </row>
     <row r="8">
@@ -3670,13 +3670,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.69662426385451</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="C8" t="n">
-        <v>287.0630287217674</v>
+        <v>261.8615651537517</v>
       </c>
       <c r="D8" t="n">
-        <v>157.8846657969721</v>
+        <v>154.3798264928109</v>
       </c>
     </row>
     <row r="9">
@@ -3684,13 +3684,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.64062358698343</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="C9" t="n">
-        <v>194.4734209865464</v>
+        <v>213.9984193286069</v>
       </c>
       <c r="D9" t="n">
-        <v>163.1890486430175</v>
+        <v>144.4406127350162</v>
       </c>
     </row>
     <row r="10">
@@ -3698,13 +3698,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.829437941368314</v>
+        <v>16.37064296831556</v>
       </c>
       <c r="C10" t="n">
-        <v>93.66854846218818</v>
+        <v>135.8051599284613</v>
       </c>
       <c r="D10" t="n">
-        <v>150.8946221427348</v>
+        <v>151.1793289769663</v>
       </c>
     </row>
     <row r="11">
@@ -3712,13 +3712,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>68.41308877043897</v>
       </c>
       <c r="D11" t="n">
-        <v>143.5786382506875</v>
+        <v>165.4352873903342</v>
       </c>
     </row>
     <row r="12">
@@ -3726,13 +3726,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.518763698469816</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>111.3036824735736</v>
+        <v>174.0069265961131</v>
       </c>
     </row>
     <row r="13">
@@ -3740,13 +3740,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.7804894248762143</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>12.48783079801943</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>74.14649536324036</v>
+        <v>177.431262588526</v>
       </c>
     </row>
     <row r="14">
@@ -3754,13 +3754,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>12.29148125717007</v>
       </c>
       <c r="D14" t="n">
-        <v>40.86917518009047</v>
+        <v>161.0184044689279</v>
       </c>
     </row>
     <row r="15">
@@ -3768,13 +3768,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>11.46681318560274</v>
+        <v>10.75013736150257</v>
       </c>
       <c r="D15" t="n">
-        <v>14.33351648200343</v>
+        <v>141.5434752597839</v>
       </c>
     </row>
     <row r="16">
@@ -3782,13 +3782,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>4.133157834879071</v>
+        <v>9.506263020221864</v>
       </c>
       <c r="D16" t="n">
-        <v>2.066578917439536</v>
+        <v>120.6882087784689</v>
       </c>
     </row>
     <row r="17">
@@ -3796,13 +3796,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>8.499971623368884</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>101.9996594804266</v>
       </c>
     </row>
     <row r="18">
@@ -3813,10 +3813,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>78.1176648269187</v>
       </c>
     </row>
     <row r="19">
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>43.93222801734051</v>
       </c>
     </row>
     <row r="20">
@@ -3841,10 +3841,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>32.27986451563512</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -3855,7 +3855,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>3.221197376376477</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -3897,13 +3897,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>14.47979688993621</v>
+        <v>14.51023106876786</v>
       </c>
       <c r="C2" t="n">
-        <v>2.158863201638736</v>
+        <v>2.332632545290422</v>
       </c>
       <c r="D2" t="n">
-        <v>25.30356532925729</v>
+        <v>24.73611515620263</v>
       </c>
     </row>
     <row r="3">
@@ -3914,10 +3914,10 @@
         <v>0.3043417883165112</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7755806863549802</v>
+        <v>0.7510369937488099</v>
       </c>
       <c r="D3" t="n">
-        <v>70.90181920070465</v>
+        <v>70.17041716104077</v>
       </c>
     </row>
     <row r="4">
@@ -3925,13 +3925,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.429424657383356</v>
       </c>
       <c r="C4" t="n">
-        <v>3.037527396939631</v>
+        <v>3.012001956629214</v>
       </c>
       <c r="D4" t="n">
-        <v>152.9484383400191</v>
+        <v>151.8891325671368</v>
       </c>
     </row>
     <row r="5">
@@ -3939,13 +3939,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.092505268377454</v>
+        <v>3.018874190558943</v>
       </c>
       <c r="C5" t="n">
-        <v>4.147884050442775</v>
+        <v>4.172427743048945</v>
       </c>
       <c r="D5" t="n">
-        <v>86.41834166632549</v>
+        <v>89.38812847167209</v>
       </c>
     </row>
     <row r="6">
@@ -3953,13 +3953,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4.669192081397831</v>
+        <v>4.548437113775473</v>
       </c>
       <c r="C6" t="n">
-        <v>5.071708640139024</v>
+        <v>4.950953672516666</v>
       </c>
       <c r="D6" t="n">
-        <v>106.3046231635489</v>
+        <v>104.4932986492135</v>
       </c>
     </row>
     <row r="7">
@@ -3967,13 +3967,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.28809404570082</v>
+        <v>6.168320825782709</v>
       </c>
       <c r="C7" t="n">
-        <v>6.94684675525043</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="D7" t="n">
-        <v>146.901854229563</v>
+        <v>144.6860496610779</v>
       </c>
     </row>
     <row r="8">
@@ -3981,13 +3981,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.844164156932015</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="D8" t="n">
-        <v>187.4254542177586</v>
+        <v>183.9206149135974</v>
       </c>
     </row>
     <row r="9">
@@ -3995,13 +3995,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.096874227550941</v>
+        <v>8.985936736971052</v>
       </c>
       <c r="C9" t="n">
-        <v>10.53906160508951</v>
+        <v>10.31718662392973</v>
       </c>
       <c r="D9" t="n">
-        <v>224.7593559148562</v>
+        <v>221.3202937068796</v>
       </c>
     </row>
     <row r="10">
@@ -4009,13 +4009,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.2494460323367</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>11.81533362061037</v>
+        <v>11.67298020349457</v>
       </c>
       <c r="D10" t="n">
-        <v>250.6843675409018</v>
+        <v>250.5420141237861</v>
       </c>
     </row>
     <row r="11">
@@ -4029,7 +4029,7 @@
         <v>12.9718324162131</v>
       </c>
       <c r="D11" t="n">
-        <v>280.9379047949715</v>
+        <v>279.8717267881594</v>
       </c>
     </row>
     <row r="12">
@@ -4043,7 +4043,7 @@
         <v>13.66887328622834</v>
       </c>
       <c r="D12" t="n">
-        <v>289.6499339224577</v>
+        <v>290.7347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -4051,13 +4051,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10.14636252339079</v>
+        <v>10.40652566501619</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>300.2282654357171</v>
+        <v>300.4884285773425</v>
       </c>
     </row>
     <row r="14">
@@ -4065,13 +4065,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>296.2246982977986</v>
+        <v>302.6777259578129</v>
       </c>
     </row>
     <row r="15">
@@ -4079,13 +4079,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="D15" t="n">
-        <v>302.4371977702724</v>
+        <v>304.2288873305228</v>
       </c>
     </row>
     <row r="16">
@@ -4093,13 +4093,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
-        <v>288.4944168745592</v>
+        <v>301.3072061626843</v>
       </c>
     </row>
     <row r="17">
@@ -4107,13 +4107,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14.63884001802419</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>23.61103228713579</v>
+        <v>22.66659099565036</v>
       </c>
       <c r="D17" t="n">
-        <v>246.4991770776977</v>
+        <v>261.6102377414646</v>
       </c>
     </row>
     <row r="18">
@@ -4121,13 +4121,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>15.51652246562084</v>
+        <v>14.98146996680633</v>
       </c>
       <c r="C18" t="n">
-        <v>27.28767743954009</v>
+        <v>25.68251994309656</v>
       </c>
       <c r="D18" t="n">
-        <v>211.8807895305466</v>
+        <v>229.5375219914255</v>
       </c>
     </row>
     <row r="19">
@@ -4135,13 +4135,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
       <c r="C19" t="n">
-        <v>30.09056713516474</v>
+        <v>28.88694444975815</v>
       </c>
       <c r="D19" t="n">
-        <v>157.6745717882632</v>
+        <v>187.7651389234279</v>
       </c>
     </row>
     <row r="20">
@@ -4149,13 +4149,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>16.13993225781756</v>
+        <v>16.81242943522663</v>
       </c>
       <c r="C20" t="n">
-        <v>51.10978548308893</v>
+        <v>32.27986451563512</v>
       </c>
       <c r="D20" t="n">
-        <v>71.28470080536088</v>
+        <v>126.4294693529042</v>
       </c>
     </row>
     <row r="21">
@@ -4163,13 +4163,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>6.39237681036558</v>
+        <v>22.26982831603881</v>
       </c>
       <c r="C21" t="n">
-        <v>2.84105636016248</v>
+        <v>46.84343197511612</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>9.21510137215399</v>
       </c>
     </row>
   </sheetData>
@@ -4211,10 +4211,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>37.00207097306228</v>
+        <v>33.71027092072273</v>
       </c>
       <c r="D2" t="n">
-        <v>156.5337809559284</v>
+        <v>153.0407226242183</v>
       </c>
     </row>
     <row r="3">
@@ -4225,10 +4225,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>96.74632751500194</v>
+        <v>88.799079849124</v>
       </c>
       <c r="D3" t="n">
-        <v>458.4958128373453</v>
+        <v>433.1274521596078</v>
       </c>
     </row>
     <row r="4">
@@ -4236,13 +4236,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.02552544031041707</v>
+        <v>0.0765763209312512</v>
       </c>
       <c r="C4" t="n">
-        <v>199.0473835406323</v>
+        <v>175.6916056566007</v>
       </c>
       <c r="D4" t="n">
-        <v>640.841704433331</v>
+        <v>563.180552288887</v>
       </c>
     </row>
     <row r="5">
@@ -4250,13 +4250,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8099418560036188</v>
+        <v>1.153553552490002</v>
       </c>
       <c r="C5" t="n">
-        <v>283.8478049903591</v>
+        <v>233.5577788403162</v>
       </c>
       <c r="D5" t="n">
-        <v>550.4904814637929</v>
+        <v>490.8493084307991</v>
       </c>
     </row>
     <row r="6">
@@ -4264,13 +4264,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4.910702016642547</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>332.8006907672178</v>
+        <v>270.2496175388365</v>
       </c>
       <c r="D6" t="n">
-        <v>341.7365583712723</v>
+        <v>358.52149887078</v>
       </c>
     </row>
     <row r="7">
@@ -4278,13 +4278,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.07335334037803</v>
+        <v>13.65414707066464</v>
       </c>
       <c r="C7" t="n">
-        <v>349.0191628413751</v>
+        <v>294.8816674383889</v>
       </c>
       <c r="D7" t="n">
-        <v>196.8472869354152</v>
+        <v>231.6414073216264</v>
       </c>
     </row>
     <row r="8">
@@ -4292,13 +4292,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.69524160552276</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>318.8569281238003</v>
+        <v>283.5581894176062</v>
       </c>
       <c r="D8" t="n">
-        <v>159.3032912296087</v>
+        <v>159.7205340039136</v>
       </c>
     </row>
     <row r="9">
@@ -4306,13 +4306,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.41718602104266</v>
+        <v>23.51874800293658</v>
       </c>
       <c r="C9" t="n">
-        <v>225.5359183489154</v>
+        <v>241.9546669547391</v>
       </c>
       <c r="D9" t="n">
-        <v>161.9687362466387</v>
+        <v>145.1062376784955</v>
       </c>
     </row>
     <row r="10">
@@ -4320,13 +4320,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.683558444063038</v>
+        <v>17.79417713947344</v>
       </c>
       <c r="C10" t="n">
-        <v>114.3097939439774</v>
+        <v>162.9946625975767</v>
       </c>
       <c r="D10" t="n">
-        <v>149.0440277202295</v>
+        <v>150.04050164004</v>
       </c>
     </row>
     <row r="11">
@@ -4334,13 +4334,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>10.66178006812036</v>
       </c>
       <c r="C11" t="n">
-        <v>42.46942393801276</v>
+        <v>88.67047089986765</v>
       </c>
       <c r="D11" t="n">
-        <v>137.7146592132213</v>
+        <v>163.4806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4348,13 +4348,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.301797455831271</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>41.65751858660066</v>
       </c>
       <c r="D12" t="n">
-        <v>105.4455939223329</v>
+        <v>172.0542304123663</v>
       </c>
     </row>
     <row r="13">
@@ -4362,13 +4362,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>68.42290624748146</v>
+        <v>175.6101205971482</v>
       </c>
     </row>
     <row r="14">
@@ -4376,13 +4376,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>35.33800861436394</v>
+        <v>160.4038304060694</v>
       </c>
     </row>
     <row r="15">
@@ -4390,13 +4390,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>10.39179944945249</v>
+        <v>11.10847527355266</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>142.6184889959341</v>
       </c>
     </row>
     <row r="16">
@@ -4404,13 +4404,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>3.306526267903257</v>
+        <v>9.506263020221864</v>
       </c>
       <c r="D16" t="n">
-        <v>1.239947350463722</v>
+        <v>120.274892994981</v>
       </c>
     </row>
     <row r="17">
@@ -4418,13 +4418,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>8.499971623368884</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>101.5274388346839</v>
       </c>
     </row>
     <row r="18">
@@ -4435,10 +4435,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>78.1176648269187</v>
       </c>
     </row>
     <row r="19">
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>45.13585070274711</v>
       </c>
     </row>
     <row r="20">
@@ -4463,10 +4463,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>33.62485887045325</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -4477,10 +4477,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>2.8690066792801</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.3586258349100125</v>
       </c>
     </row>
   </sheetData>
@@ -4522,10 +4522,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>29.64583542514093</v>
+        <v>27.56747553525043</v>
       </c>
       <c r="D2" t="n">
-        <v>172.5352867874472</v>
+        <v>166.1706164208151</v>
       </c>
     </row>
     <row r="3">
@@ -4536,10 +4536,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>109.2390670515426</v>
+        <v>96.65306148309848</v>
       </c>
       <c r="D3" t="n">
-        <v>453.1698315418064</v>
+        <v>427.5805776306133</v>
       </c>
     </row>
     <row r="4">
@@ -4547,13 +4547,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.01276272015520854</v>
+        <v>0.0382881604656256</v>
       </c>
       <c r="C4" t="n">
-        <v>208.5045591756418</v>
+        <v>182.5324236597925</v>
       </c>
       <c r="D4" t="n">
-        <v>664.5548384817084</v>
+        <v>573.0716604091735</v>
       </c>
     </row>
     <row r="5">
@@ -4561,13 +4561,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5890486225480863</v>
+        <v>0.8344855486097891</v>
       </c>
       <c r="C5" t="n">
-        <v>301.6665258224387</v>
+        <v>246.2223242251001</v>
       </c>
       <c r="D5" t="n">
-        <v>566.4684253504097</v>
+        <v>505.3055433758334</v>
       </c>
     </row>
     <row r="6">
@@ -4575,13 +4575,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3.944662275663684</v>
+        <v>4.387430490278996</v>
       </c>
       <c r="C6" t="n">
-        <v>363.6737108226673</v>
+        <v>287.4370745970854</v>
       </c>
       <c r="D6" t="n">
-        <v>362.8686777051849</v>
+        <v>376.6347440141337</v>
       </c>
     </row>
     <row r="7">
@@ -4589,13 +4589,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.21686843164731</v>
+        <v>11.5581157220977</v>
       </c>
       <c r="C7" t="n">
-        <v>377.4653025719264</v>
+        <v>314.9436817746725</v>
       </c>
       <c r="D7" t="n">
-        <v>205.1116391097649</v>
+        <v>244.6966882927005</v>
       </c>
     </row>
     <row r="8">
@@ -4603,13 +4603,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.69385894719101</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="C8" t="n">
-        <v>351.3184159647211</v>
+        <v>304.086533913407</v>
       </c>
       <c r="D8" t="n">
-        <v>157.7177686872501</v>
+        <v>166.062624173348</v>
       </c>
     </row>
     <row r="9">
@@ -4617,13 +4617,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.74999849278232</v>
+        <v>22.96406055003713</v>
       </c>
       <c r="C9" t="n">
-        <v>256.7093532018644</v>
+        <v>264.8077900141963</v>
       </c>
       <c r="D9" t="n">
-        <v>159.1952989821415</v>
+        <v>146.1046750937145</v>
       </c>
     </row>
     <row r="10">
@@ -4631,13 +4631,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.110618695410402</v>
+        <v>18.64829764216817</v>
       </c>
       <c r="C10" t="n">
-        <v>137.0863406825034</v>
+        <v>191.60769943785</v>
       </c>
       <c r="D10" t="n">
-        <v>146.9087264634927</v>
+        <v>149.0440277202295</v>
       </c>
     </row>
     <row r="11">
@@ -4645,13 +4645,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>12.08335074386974</v>
       </c>
       <c r="C11" t="n">
-        <v>50.6434553235717</v>
+        <v>109.2832456982337</v>
       </c>
       <c r="D11" t="n">
-        <v>132.9168581825672</v>
+        <v>163.1252350422415</v>
       </c>
     </row>
     <row r="12">
@@ -4659,13 +4659,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>53.80762817435918</v>
       </c>
       <c r="D12" t="n">
-        <v>99.15357288581511</v>
+        <v>169.8845679859808</v>
       </c>
     </row>
     <row r="13">
@@ -4673,13 +4673,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>62.17899084847173</v>
+        <v>173.528815464145</v>
       </c>
     </row>
     <row r="14">
@@ -4687,13 +4687,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>159.4819693117816</v>
       </c>
     </row>
     <row r="15">
@@ -4701,13 +4701,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>9.316785713302231</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>8.958447801252145</v>
+        <v>141.901813171834</v>
       </c>
     </row>
     <row r="16">
@@ -4715,13 +4715,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>2.479894700927443</v>
+        <v>9.506263020221864</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8266315669758143</v>
+        <v>119.8615772114931</v>
       </c>
     </row>
     <row r="17">
@@ -4729,13 +4729,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>8.499971623368884</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>101.0552181889412</v>
       </c>
     </row>
     <row r="18">
@@ -4746,10 +4746,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>78.1176648269187</v>
       </c>
     </row>
     <row r="19">
@@ -4760,10 +4760,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>10.23079282595601</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>46.33947338815369</v>
       </c>
     </row>
     <row r="20">
@@ -4774,10 +4774,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>34.29735604786232</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>16.81242943522663</v>
       </c>
     </row>
     <row r="21">
@@ -4788,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>2.516746802734418</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -4833,10 +4833,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>34.60464307929157</v>
+        <v>31.07231483941155</v>
       </c>
       <c r="D2" t="n">
-        <v>159.9620439391583</v>
+        <v>153.353900141873</v>
       </c>
     </row>
     <row r="3">
@@ -4847,10 +4847,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>109.4795952390831</v>
+        <v>96.45671194224911</v>
       </c>
       <c r="D3" t="n">
-        <v>457.2489932529519</v>
+        <v>425.7250744695868</v>
       </c>
     </row>
     <row r="4">
@@ -4858,13 +4858,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>0.02552544031041707</v>
       </c>
       <c r="C4" t="n">
-        <v>222.2882969432671</v>
+        <v>189.0924618195696</v>
       </c>
       <c r="D4" t="n">
-        <v>673.9354377957866</v>
+        <v>581.1632249875759</v>
       </c>
     </row>
     <row r="5">
@@ -4872,13 +4872,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.4417864669110648</v>
+        <v>0.6135923151542566</v>
       </c>
       <c r="C5" t="n">
-        <v>317.3008580125692</v>
+        <v>259.8440736215246</v>
       </c>
       <c r="D5" t="n">
-        <v>588.8277293146308</v>
+        <v>519.4427103169875</v>
       </c>
     </row>
     <row r="6">
@@ -4886,13 +4886,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3.220132469929539</v>
+        <v>3.461642405174254</v>
       </c>
       <c r="C6" t="n">
-        <v>388.3882275293765</v>
+        <v>302.8534587968731</v>
       </c>
       <c r="D6" t="n">
-        <v>375.2259360585394</v>
+        <v>394.6674858457391</v>
       </c>
     </row>
     <row r="7">
@@ -4900,13 +4900,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.65981657271187</v>
+        <v>9.82140403328509</v>
       </c>
       <c r="C7" t="n">
-        <v>411.4210104187108</v>
+        <v>330.6938601939041</v>
       </c>
       <c r="D7" t="n">
-        <v>213.7951975538279</v>
+        <v>260.7462997617274</v>
       </c>
     </row>
     <row r="8">
@@ -4914,13 +4914,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.52557917913731</v>
+        <v>17.44074796594459</v>
       </c>
       <c r="C8" t="n">
-        <v>381.9440355987003</v>
+        <v>327.3686807196201</v>
       </c>
       <c r="D8" t="n">
-        <v>156.1322461448915</v>
+        <v>171.2364345747287</v>
       </c>
     </row>
     <row r="9">
@@ -4928,13 +4928,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.74999849278232</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="C9" t="n">
-        <v>285.8859132243753</v>
+        <v>285.4421632620558</v>
       </c>
       <c r="D9" t="n">
-        <v>157.5312366234431</v>
+        <v>146.7703000371938</v>
       </c>
     </row>
     <row r="10">
@@ -4942,13 +4942,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>19.21771131063132</v>
       </c>
       <c r="C10" t="n">
-        <v>157.1581724958294</v>
+        <v>215.2383666790707</v>
       </c>
       <c r="D10" t="n">
-        <v>143.2075376184822</v>
+        <v>147.9052003833032</v>
       </c>
     </row>
     <row r="11">
@@ -4956,13 +4956,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>12.9718324162131</v>
       </c>
       <c r="C11" t="n">
-        <v>59.70596838147401</v>
+        <v>132.2060728446924</v>
       </c>
       <c r="D11" t="n">
-        <v>127.9413608174443</v>
+        <v>160.8151826941487</v>
       </c>
     </row>
     <row r="12">
@@ -4970,13 +4970,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>6.942919764433443</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>66.60863649003335</v>
       </c>
       <c r="D12" t="n">
-        <v>93.07851809193585</v>
+        <v>167.7149055595953</v>
       </c>
     </row>
     <row r="13">
@@ -4984,13 +4984,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>31.73990327829938</v>
       </c>
       <c r="D13" t="n">
-        <v>56.19523859108743</v>
+        <v>171.4475103311417</v>
       </c>
     </row>
     <row r="14">
@@ -4998,13 +4998,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>25.81211064005714</v>
+        <v>158.2528211860646</v>
       </c>
     </row>
     <row r="15">
@@ -5012,13 +5012,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>8.241771977151972</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>141.1851373477338</v>
       </c>
     </row>
     <row r="16">
@@ -5026,13 +5026,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>1.653263133951629</v>
+        <v>9.919578803709772</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4133157834879072</v>
+        <v>120.6882087784689</v>
       </c>
     </row>
     <row r="17">
@@ -5040,13 +5040,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>8.499971623368884</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>100.1107768974558</v>
       </c>
     </row>
     <row r="18">
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>8.025787482217675</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>77.58261232810419</v>
       </c>
     </row>
     <row r="19">
@@ -5071,10 +5071,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>9.628981483252716</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>46.94128473085699</v>
       </c>
     </row>
     <row r="20">
@@ -5085,10 +5085,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>34.29735604786232</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>17.48492661263569</v>
       </c>
     </row>
     <row r="21">
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>2.521751108862941</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -5144,10 +5144,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>52.23781359526853</v>
+        <v>44.57919975443917</v>
       </c>
       <c r="D2" t="n">
-        <v>191.5448675847782</v>
+        <v>178.5641994392269</v>
       </c>
     </row>
     <row r="3">
@@ -5158,10 +5158,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>113.0924267907113</v>
+        <v>98.6165568915921</v>
       </c>
       <c r="D3" t="n">
-        <v>451.0099865924635</v>
+        <v>425.0623947692203</v>
       </c>
     </row>
     <row r="4">
@@ -5169,13 +5169,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>0.01276272015520854</v>
       </c>
       <c r="C4" t="n">
-        <v>232.0262524216911</v>
+        <v>192.7808879444249</v>
       </c>
       <c r="D4" t="n">
-        <v>689.5697699859171</v>
+        <v>583.1414466116331</v>
       </c>
     </row>
     <row r="5">
@@ -5183,13 +5183,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.3190680038802134</v>
+        <v>0.466330159517235</v>
       </c>
       <c r="C5" t="n">
-        <v>333.9660252921587</v>
+        <v>268.3607349558657</v>
       </c>
       <c r="D5" t="n">
-        <v>598.080701427157</v>
+        <v>527.3703230287805</v>
       </c>
     </row>
     <row r="6">
@@ -5197,13 +5197,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.61635763181775</v>
+        <v>2.777364255314227</v>
       </c>
       <c r="C6" t="n">
-        <v>415.7996051796517</v>
+        <v>321.0874589078491</v>
       </c>
       <c r="D6" t="n">
-        <v>391.8498699345507</v>
+        <v>408.3127971870655</v>
       </c>
     </row>
     <row r="7">
@@ -5211,13 +5211,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.282424543653592</v>
+        <v>8.26435217434965</v>
       </c>
       <c r="C7" t="n">
-        <v>438.9688509998763</v>
+        <v>345.1864198039955</v>
       </c>
       <c r="D7" t="n">
-        <v>217.148847711535</v>
+        <v>271.5258895543573</v>
       </c>
     </row>
     <row r="8">
@@ -5225,13 +5225,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.35729941108361</v>
+        <v>15.60487975900305</v>
       </c>
       <c r="C8" t="n">
-        <v>413.6544864458723</v>
+        <v>344.3087373563989</v>
       </c>
       <c r="D8" t="n">
-        <v>155.7150033705866</v>
+        <v>177.1612819698582</v>
       </c>
     </row>
     <row r="9">
@@ -5239,13 +5239,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.52812351162255</v>
+        <v>20.30156077611979</v>
       </c>
       <c r="C9" t="n">
-        <v>314.6187232845667</v>
+        <v>308.8499737744124</v>
       </c>
       <c r="D9" t="n">
-        <v>154.3140493966264</v>
+        <v>147.7687374524129</v>
       </c>
     </row>
     <row r="10">
@@ -5253,13 +5253,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>19.07535789351553</v>
       </c>
       <c r="C10" t="n">
-        <v>177.0876508920397</v>
+        <v>236.0219655779757</v>
       </c>
       <c r="D10" t="n">
-        <v>140.5028226932823</v>
+        <v>146.9087264634927</v>
       </c>
     </row>
     <row r="11">
@@ -5267,13 +5267,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.665445017030089</v>
+        <v>13.68261775408779</v>
       </c>
       <c r="C11" t="n">
-        <v>68.94617777384498</v>
+        <v>152.2857586396524</v>
       </c>
       <c r="D11" t="n">
-        <v>121.7219891110407</v>
+        <v>158.6828266805247</v>
       </c>
     </row>
     <row r="12">
@@ -5281,13 +5281,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.6508987279156353</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>80.92840850417731</v>
       </c>
       <c r="D12" t="n">
-        <v>87.00346329805657</v>
+        <v>165.7622093758484</v>
       </c>
     </row>
     <row r="13">
@@ -5295,13 +5295,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>3.642283982755667</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>39.28463438543612</v>
       </c>
       <c r="D13" t="n">
-        <v>50.73181261695393</v>
+        <v>170.927184047891</v>
       </c>
     </row>
     <row r="14">
@@ -5309,13 +5309,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>21.51009220004762</v>
+        <v>156.7163860289184</v>
       </c>
     </row>
     <row r="15">
@@ -5323,13 +5323,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>7.166758241001715</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>5.0167307687012</v>
+        <v>139.7517856995334</v>
       </c>
     </row>
     <row r="16">
@@ -5337,13 +5337,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>1.239947350463722</v>
+        <v>10.33289458719768</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>119.8615772114931</v>
       </c>
     </row>
     <row r="17">
@@ -5354,10 +5354,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>8.499971623368884</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>99.16633560597033</v>
       </c>
     </row>
     <row r="18">
@@ -5368,10 +5368,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>8.025787482217675</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>77.04755982928968</v>
       </c>
     </row>
     <row r="19">
@@ -5382,10 +5382,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>9.027170140549421</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>47.54309607356029</v>
       </c>
     </row>
     <row r="20">
@@ -5396,10 +5396,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>34.29735604786232</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>18.15742379004475</v>
       </c>
     </row>
     <row r="21">
@@ -5410,10 +5410,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>2.165703469142401</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.3609505781904001</v>
       </c>
     </row>
   </sheetData>
@@ -5455,10 +5455,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>50.97430429990289</v>
+        <v>43.64850293081319</v>
       </c>
       <c r="D2" t="n">
-        <v>157.3623760183127</v>
+        <v>147.3721113798972</v>
       </c>
     </row>
     <row r="3">
@@ -5469,10 +5469,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>132.7421070912112</v>
+        <v>109.7250321651448</v>
       </c>
       <c r="D3" t="n">
-        <v>457.2882631611218</v>
+        <v>423.3688799793945</v>
       </c>
     </row>
     <row r="4">
@@ -5483,10 +5483,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>240.2964950822663</v>
+        <v>197.9115014468188</v>
       </c>
       <c r="D4" t="n">
-        <v>691.7904832929235</v>
+        <v>584.8644138325863</v>
       </c>
     </row>
     <row r="5">
@@ -5494,13 +5494,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2454369260617026</v>
+        <v>0.3436116964863837</v>
       </c>
       <c r="C5" t="n">
-        <v>348.5449787002239</v>
+        <v>274.324852259165</v>
       </c>
       <c r="D5" t="n">
-        <v>613.5923151542565</v>
+        <v>534.7825181958439</v>
       </c>
     </row>
     <row r="6">
@@ -5508,13 +5508,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.173589417202439</v>
+        <v>2.213841073076558</v>
       </c>
       <c r="C6" t="n">
-        <v>436.8914728576902</v>
+        <v>332.9616973907143</v>
       </c>
       <c r="D6" t="n">
-        <v>400.4234726357382</v>
+        <v>421.636095281399</v>
       </c>
     </row>
     <row r="7">
@@ -5522,13 +5522,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.144578954431539</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>471.2477337678072</v>
+        <v>363.6913822813436</v>
       </c>
       <c r="D7" t="n">
-        <v>219.6640853298153</v>
+        <v>282.5450257868235</v>
       </c>
     </row>
     <row r="8">
@@ -5536,13 +5536,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.10557108816892</v>
+        <v>13.76901155206151</v>
       </c>
       <c r="C8" t="n">
-        <v>442.694583537493</v>
+        <v>358.8287859022092</v>
       </c>
       <c r="D8" t="n">
-        <v>153.6287894990621</v>
+        <v>183.4199235844316</v>
       </c>
     </row>
     <row r="9">
@@ -5550,13 +5550,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.19531103988288</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="C9" t="n">
-        <v>340.5780960802609</v>
+        <v>325.9343473237154</v>
       </c>
       <c r="D9" t="n">
-        <v>151.0968621698096</v>
+        <v>150.5421747169101</v>
       </c>
     </row>
     <row r="10">
@@ -5564,13 +5564,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>18.79065105928395</v>
       </c>
       <c r="C10" t="n">
-        <v>194.1700609459342</v>
+        <v>256.3785042255333</v>
       </c>
       <c r="D10" t="n">
-        <v>137.5134009338507</v>
+        <v>145.6275457094506</v>
       </c>
     </row>
     <row r="11">
@@ -5578,13 +5578,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.310052348092745</v>
+        <v>14.03801042302514</v>
       </c>
       <c r="C11" t="n">
-        <v>75.87633481812323</v>
+        <v>172.8985334380185</v>
       </c>
       <c r="D11" t="n">
-        <v>116.3910990769806</v>
+        <v>156.3727743324319</v>
       </c>
     </row>
     <row r="12">
@@ -5592,13 +5592,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4339324852770902</v>
+        <v>8.244717220264713</v>
       </c>
       <c r="C12" t="n">
-        <v>22.78145547704723</v>
+        <v>94.59728179040565</v>
       </c>
       <c r="D12" t="n">
-        <v>80.71144226153876</v>
+        <v>163.3755807068245</v>
       </c>
     </row>
     <row r="13">
@@ -5606,13 +5606,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>46.82936549257286</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>168.5857157732623</v>
       </c>
     </row>
     <row r="14">
@@ -5620,13 +5620,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>17.8226478228966</v>
+        <v>155.1799508717721</v>
       </c>
     </row>
     <row r="15">
@@ -5634,13 +5634,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>6.091744504851459</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>3.583379120500858</v>
+        <v>138.3184340513331</v>
       </c>
     </row>
     <row r="16">
@@ -5648,13 +5648,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8266315669758143</v>
+        <v>10.74621037068559</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>119.0349456445173</v>
       </c>
     </row>
     <row r="17">
@@ -5665,10 +5665,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>8.499971623368884</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>98.2218943144849</v>
       </c>
     </row>
     <row r="18">
@@ -5679,10 +5679,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>8.025787482217675</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>77.58261232810419</v>
       </c>
     </row>
     <row r="19">
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>8.425358797846126</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>47.54309607356029</v>
       </c>
     </row>
     <row r="20">
@@ -5707,10 +5707,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>34.29735604786232</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>18.82992096745382</v>
       </c>
     </row>
     <row r="21">
@@ -5721,7 +5721,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>2.170816263757179</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -5766,10 +5766,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>60.58463257677491</v>
+        <v>50.29984362708533</v>
       </c>
       <c r="D2" t="n">
-        <v>176.4976205217873</v>
+        <v>162.578401570976</v>
       </c>
     </row>
     <row r="3">
@@ -5780,10 +5780,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>143.4873357141926</v>
+        <v>117.1077749010808</v>
       </c>
       <c r="D3" t="n">
-        <v>454.8093502078986</v>
+        <v>415.5836206847173</v>
       </c>
     </row>
     <row r="4">
@@ -5794,10 +5794,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>256.4285733584499</v>
+        <v>206.1434559469283</v>
       </c>
       <c r="D4" t="n">
-        <v>694.6110444472246</v>
+        <v>586.2300248891936</v>
       </c>
     </row>
     <row r="5">
@@ -5805,13 +5805,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1718058482431918</v>
+        <v>0.2454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>361.9949222484052</v>
+        <v>279.6753772473102</v>
       </c>
       <c r="D5" t="n">
-        <v>628.3430744105649</v>
+        <v>541.703839510784</v>
       </c>
     </row>
     <row r="6">
@@ -5819,13 +5819,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.811324514335366</v>
+        <v>1.771072858461246</v>
       </c>
       <c r="C6" t="n">
-        <v>457.1783074182463</v>
+        <v>343.1856179827406</v>
       </c>
       <c r="D6" t="n">
-        <v>409.2385852721702</v>
+        <v>438.7430490278996</v>
       </c>
     </row>
     <row r="7">
@@ -5833,13 +5833,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.186393195086651</v>
+        <v>5.988660995905543</v>
       </c>
       <c r="C7" t="n">
-        <v>501.9096780668435</v>
+        <v>380.5794062897972</v>
       </c>
       <c r="D7" t="n">
-        <v>222.1793229480956</v>
+        <v>290.3901716914598</v>
       </c>
     </row>
     <row r="8">
@@ -5847,13 +5847,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.85384276525424</v>
+        <v>12.10004045484194</v>
       </c>
       <c r="C8" t="n">
-        <v>471.9850262936965</v>
+        <v>373.3488344480195</v>
       </c>
       <c r="D8" t="n">
-        <v>151.5425756275376</v>
+        <v>187.9261455469244</v>
       </c>
     </row>
     <row r="9">
@@ -5861,13 +5861,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.75156107756332</v>
+        <v>17.19531103988288</v>
       </c>
       <c r="C9" t="n">
-        <v>362.2109067433394</v>
+        <v>341.5765334954799</v>
       </c>
       <c r="D9" t="n">
-        <v>148.9890498487916</v>
+        <v>151.0968621698096</v>
       </c>
     </row>
     <row r="10">
@@ -5875,13 +5875,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>18.2212373908208</v>
       </c>
       <c r="C10" t="n">
-        <v>214.5265995934918</v>
+        <v>275.0268018677015</v>
       </c>
       <c r="D10" t="n">
-        <v>133.1004450032613</v>
+        <v>144.4887183725243</v>
       </c>
     </row>
     <row r="11">
@@ -5889,13 +5889,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.954659679155399</v>
+        <v>14.03801042302514</v>
       </c>
       <c r="C11" t="n">
-        <v>81.91801019005808</v>
+        <v>192.6228265640411</v>
       </c>
       <c r="D11" t="n">
-        <v>111.0602090429204</v>
+        <v>154.2404183188078</v>
       </c>
     </row>
     <row r="12">
@@ -5903,13 +5903,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2169662426385451</v>
+        <v>8.678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>108.4831213192725</v>
       </c>
       <c r="D12" t="n">
-        <v>74.6363874676595</v>
+        <v>160.9889520378005</v>
       </c>
     </row>
     <row r="13">
@@ -5917,13 +5917,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>12.48783079801943</v>
+        <v>54.89442288296041</v>
       </c>
       <c r="D13" t="n">
-        <v>39.80496066868693</v>
+        <v>166.2442474986337</v>
       </c>
     </row>
     <row r="14">
@@ -5931,13 +5931,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>10.44775906859456</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>153.6435157146258</v>
       </c>
     </row>
     <row r="15">
@@ -5945,13 +5945,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>5.0167307687012</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>136.8850824031328</v>
       </c>
     </row>
     <row r="16">
@@ -5959,13 +5959,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4133157834879072</v>
+        <v>11.15952615417349</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>119.0349456445173</v>
       </c>
     </row>
     <row r="17">
@@ -5976,10 +5976,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>8.499971623368884</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>97.27745302299945</v>
       </c>
     </row>
     <row r="18">
@@ -5990,10 +5990,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>8.025787482217675</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>76.51250733047517</v>
       </c>
     </row>
     <row r="19">
@@ -6004,10 +6004,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>7.823547455142832</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>47.54309607356029</v>
       </c>
     </row>
     <row r="20">
@@ -6018,10 +6018,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>34.29735604786232</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>18.82992096745382</v>
       </c>
     </row>
     <row r="21">
@@ -6032,7 +6032,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.81234287259186</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -6077,10 +6077,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>75.69176624972484</v>
+        <v>61.36904899246812</v>
       </c>
       <c r="D2" t="n">
-        <v>182.2231731329547</v>
+        <v>166.1519632144344</v>
       </c>
     </row>
     <row r="3">
@@ -6091,10 +6091,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>160.0396020077938</v>
+        <v>125.7373372214102</v>
       </c>
       <c r="D3" t="n">
-        <v>454.4510122958486</v>
+        <v>409.0108198047849</v>
       </c>
     </row>
     <row r="4">
@@ -6105,10 +6105,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>272.3692108323053</v>
+        <v>212.0525953787898</v>
       </c>
       <c r="D4" t="n">
-        <v>692.2244157782005</v>
+        <v>581.7503101147154</v>
       </c>
     </row>
     <row r="5">
@@ -6116,13 +6116,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1227184630308513</v>
+        <v>0.1718058482431918</v>
       </c>
       <c r="C5" t="n">
-        <v>375.8621085708914</v>
+        <v>285.2958828541231</v>
       </c>
       <c r="D5" t="n">
-        <v>629.5948027334796</v>
+        <v>542.5137813667875</v>
       </c>
     </row>
     <row r="6">
@@ -6130,13 +6130,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.489311267342412</v>
+        <v>1.449059611468292</v>
       </c>
       <c r="C6" t="n">
-        <v>475.2513009057258</v>
+        <v>355.2611147449763</v>
       </c>
       <c r="D6" t="n">
-        <v>422.2801217753849</v>
+        <v>446.8738835144717</v>
       </c>
     </row>
     <row r="7">
@@ -6144,13 +6144,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.347980655659875</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>524.3671568014894</v>
+        <v>390.7601299828367</v>
       </c>
       <c r="D7" t="n">
-        <v>218.7058995704705</v>
+        <v>298.7742970857275</v>
       </c>
     </row>
     <row r="8">
@@ -6158,13 +6158,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.76901155206151</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>500.8582262755953</v>
+        <v>387.368191664664</v>
       </c>
       <c r="D8" t="n">
-        <v>150.6246415240669</v>
+        <v>192.5992646191393</v>
       </c>
     </row>
     <row r="9">
@@ -6172,13 +6172,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.30781111524376</v>
+        <v>15.8640611529242</v>
       </c>
       <c r="C9" t="n">
-        <v>386.3952796897552</v>
+        <v>355.8874697802856</v>
       </c>
       <c r="D9" t="n">
-        <v>145.3281126596553</v>
+        <v>151.8734246038688</v>
       </c>
     </row>
     <row r="10">
@@ -6186,13 +6186,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.398851609831464</v>
+        <v>17.22476347101029</v>
       </c>
       <c r="C10" t="n">
-        <v>228.7619413050705</v>
+        <v>294.5292200125643</v>
       </c>
       <c r="D10" t="n">
-        <v>128.6874890726719</v>
+        <v>143.4922444527138</v>
       </c>
     </row>
     <row r="11">
@@ -6200,13 +6200,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>13.86031408855647</v>
       </c>
       <c r="C11" t="n">
-        <v>86.18272221730622</v>
+        <v>207.904711328347</v>
       </c>
       <c r="D11" t="n">
-        <v>105.7293190088602</v>
+        <v>152.1080623051838</v>
       </c>
     </row>
     <row r="12">
@@ -6214,13 +6214,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>9.112582190818895</v>
       </c>
       <c r="C12" t="n">
-        <v>21.47965802121596</v>
+        <v>122.3689608481394</v>
       </c>
       <c r="D12" t="n">
-        <v>68.77829891641879</v>
+        <v>158.819289611415</v>
       </c>
     </row>
     <row r="13">
@@ -6228,13 +6228,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>12.22766765639403</v>
+        <v>63.21964341497336</v>
       </c>
       <c r="D13" t="n">
-        <v>34.86186097780424</v>
+        <v>165.4637580737574</v>
       </c>
     </row>
     <row r="14">
@@ -6242,13 +6242,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>9.525897974306801</v>
+        <v>31.65056423721292</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>151.7997935260503</v>
       </c>
     </row>
     <row r="15">
@@ -6256,13 +6256,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>3.941717032550943</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="D15" t="n">
-        <v>1.791689560250429</v>
+        <v>135.0933928428823</v>
       </c>
     </row>
     <row r="16">
@@ -6270,13 +6270,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>11.5728419376614</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>117.7949982940535</v>
       </c>
     </row>
     <row r="17">
@@ -6287,10 +6287,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>8.499971623368884</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>96.33301173151402</v>
       </c>
     </row>
     <row r="18">
@@ -6301,10 +6301,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>8.025787482217675</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>75.44240233284614</v>
       </c>
     </row>
     <row r="19">
@@ -6315,10 +6315,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>7.221736112439537</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>47.54309607356029</v>
       </c>
     </row>
     <row r="20">
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>33.62485887045325</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>18.82992096745382</v>
       </c>
     </row>
     <row r="21">
@@ -6343,7 +6343,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.815517010206974</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -6388,10 +6388,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>65.49238935030472</v>
+        <v>54.10804297185871</v>
       </c>
       <c r="D2" t="n">
-        <v>162.9779728866045</v>
+        <v>148.4697053132451</v>
       </c>
     </row>
     <row r="3">
@@ -6402,10 +6402,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>183.5082808778138</v>
+        <v>138.1711718956961</v>
       </c>
       <c r="D3" t="n">
-        <v>455.2658628903733</v>
+        <v>403.5277588765665</v>
       </c>
     </row>
     <row r="4">
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>291.5388165054285</v>
+        <v>219.0082778633785</v>
       </c>
       <c r="D4" t="n">
-        <v>689.9654143107286</v>
+        <v>576.9642900565123</v>
       </c>
     </row>
     <row r="5">
@@ -6427,13 +6427,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.09817477042468106</v>
+        <v>0.1227184630308513</v>
       </c>
       <c r="C5" t="n">
-        <v>390.7601299828368</v>
+        <v>290.3273398383881</v>
       </c>
       <c r="D5" t="n">
-        <v>630.6501815155449</v>
+        <v>542.9310241410924</v>
       </c>
     </row>
     <row r="6">
@@ -6441,13 +6441,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.247801332097696</v>
+        <v>1.167298020349458</v>
       </c>
       <c r="C6" t="n">
-        <v>492.6802678992194</v>
+        <v>365.7667969281214</v>
       </c>
       <c r="D6" t="n">
-        <v>436.5292079548231</v>
+        <v>454.5619497864285</v>
       </c>
     </row>
     <row r="7">
@@ -6455,13 +6455,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.629341336151211</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>545.626903336954</v>
+        <v>400.4617607962036</v>
       </c>
       <c r="D7" t="n">
-        <v>214.2742904335003</v>
+        <v>307.0985358700362</v>
       </c>
     </row>
     <row r="8">
@@ -6469,13 +6469,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.76762889372977</v>
+        <v>9.429686699290613</v>
       </c>
       <c r="C8" t="n">
-        <v>528.0624551602743</v>
+        <v>399.6351292292279</v>
       </c>
       <c r="D8" t="n">
-        <v>148.1211848782375</v>
+        <v>197.439280801076</v>
       </c>
     </row>
     <row r="9">
@@ -6483,13 +6483,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.8640611529242</v>
+        <v>14.53281126596553</v>
       </c>
       <c r="C9" t="n">
-        <v>409.1374652586326</v>
+        <v>368.9780936687126</v>
       </c>
       <c r="D9" t="n">
-        <v>141.6671754705189</v>
+        <v>152.8718620190878</v>
       </c>
     </row>
     <row r="10">
@@ -6497,13 +6497,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>16.22828955119978</v>
       </c>
       <c r="C10" t="n">
-        <v>242.0008090968388</v>
+        <v>312.181043734922</v>
       </c>
       <c r="D10" t="n">
-        <v>125.1286536447772</v>
+        <v>142.4957705329033</v>
       </c>
     </row>
     <row r="11">
@@ -6511,13 +6511,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.243874341280709</v>
+        <v>13.50492141961912</v>
       </c>
       <c r="C11" t="n">
-        <v>87.0712038896496</v>
+        <v>222.4758107547781</v>
       </c>
       <c r="D11" t="n">
-        <v>99.332250967988</v>
+        <v>151.5749733017778</v>
       </c>
     </row>
     <row r="12">
@@ -6525,13 +6525,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>9.112582190818895</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>135.1699691638136</v>
       </c>
       <c r="D12" t="n">
-        <v>63.13717660781662</v>
+        <v>156.432660942391</v>
       </c>
     </row>
     <row r="13">
@@ -6539,13 +6539,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>71.54486394698631</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>162.8621266575034</v>
       </c>
     </row>
     <row r="14">
@@ -6553,13 +6553,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>8.604036880019047</v>
+        <v>36.2598697086517</v>
       </c>
       <c r="D14" t="n">
-        <v>9.833185005736054</v>
+        <v>149.9560713374748</v>
       </c>
     </row>
     <row r="15">
@@ -6567,13 +6567,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>3.225041208450772</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
-        <v>1.075013736150257</v>
+        <v>133.3017032826319</v>
       </c>
     </row>
     <row r="16">
@@ -6581,13 +6581,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>116.5550509435898</v>
       </c>
     </row>
     <row r="17">
@@ -6598,10 +6598,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>8.499971623368884</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>95.3885704400286</v>
       </c>
     </row>
     <row r="18">
@@ -6612,10 +6612,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>8.025787482217675</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>74.90734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -6626,10 +6626,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>7.221736112439537</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>47.54309607356029</v>
       </c>
     </row>
     <row r="20">
@@ -6640,10 +6640,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>33.62485887045325</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>18.82992096745382</v>
       </c>
     </row>
     <row r="21">
@@ -6654,7 +6654,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.454855101532468</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -6699,10 +6699,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>8.947648576505429</v>
+        <v>9.852819959820989</v>
       </c>
       <c r="D2" t="n">
-        <v>93.75985099868312</v>
+        <v>90.32078879070656</v>
       </c>
     </row>
     <row r="3">
@@ -6710,13 +6710,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.16786316189298</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="C3" t="n">
-        <v>3.750276230222816</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="D3" t="n">
-        <v>72.06028149171588</v>
+        <v>70.51893759604839</v>
       </c>
     </row>
     <row r="4">
@@ -6724,13 +6724,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.084831213192726</v>
+        <v>1.021017612416683</v>
       </c>
       <c r="C4" t="n">
-        <v>2.603594911662541</v>
+        <v>2.514255870576081</v>
       </c>
       <c r="D4" t="n">
-        <v>151.0085048764274</v>
+        <v>148.7367406888003</v>
       </c>
     </row>
     <row r="5">
@@ -6738,13 +6738,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2.79798095710341</v>
+        <v>2.626175108860218</v>
       </c>
       <c r="C5" t="n">
-        <v>4.66330159517235</v>
+        <v>4.61421420996001</v>
       </c>
       <c r="D5" t="n">
-        <v>100.5555086074796</v>
+        <v>105.2678975878643</v>
       </c>
     </row>
     <row r="6">
@@ -6752,13 +6752,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4.588688769649592</v>
+        <v>4.347178834404877</v>
       </c>
       <c r="C6" t="n">
-        <v>5.594980166502573</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="D6" t="n">
-        <v>107.1096562810313</v>
+        <v>106.2241198518007</v>
       </c>
     </row>
     <row r="7">
@@ -6766,13 +6766,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.168320825782709</v>
+        <v>5.868887775987432</v>
       </c>
       <c r="C7" t="n">
-        <v>7.126506585127596</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="D7" t="n">
-        <v>148.8182257482527</v>
+        <v>142.8295647523472</v>
       </c>
     </row>
     <row r="8">
@@ -6780,13 +6780,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.677267047210056</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>9.012443924985718</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="D8" t="n">
-        <v>190.9302935219197</v>
+        <v>183.7537178038755</v>
       </c>
     </row>
     <row r="9">
@@ -6794,13 +6794,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
-        <v>10.98281156740907</v>
+        <v>10.42812411450962</v>
       </c>
       <c r="D9" t="n">
-        <v>223.4281060278975</v>
+        <v>218.879668914122</v>
       </c>
     </row>
     <row r="10">
@@ -6808,13 +6808,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.680032363873552</v>
       </c>
       <c r="C10" t="n">
-        <v>12.24239387195773</v>
+        <v>11.95768703772615</v>
       </c>
       <c r="D10" t="n">
-        <v>251.253781209365</v>
+        <v>248.4067128670492</v>
       </c>
     </row>
     <row r="11">
@@ -6825,10 +6825,10 @@
         <v>10.30638739918301</v>
       </c>
       <c r="C11" t="n">
-        <v>13.32722508515045</v>
+        <v>13.14952875068177</v>
       </c>
       <c r="D11" t="n">
-        <v>279.1609414502847</v>
+        <v>277.0285854366606</v>
       </c>
     </row>
     <row r="12">
@@ -6839,10 +6839,10 @@
         <v>10.41437964665016</v>
       </c>
       <c r="C12" t="n">
-        <v>14.31977201414398</v>
+        <v>14.10280577150543</v>
       </c>
       <c r="D12" t="n">
-        <v>287.2633052534337</v>
+        <v>289.2160014371806</v>
       </c>
     </row>
     <row r="13">
@@ -6850,13 +6850,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9.886199381765381</v>
+        <v>10.14636252339079</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>297.6266340194631</v>
+        <v>301.5290811438442</v>
       </c>
     </row>
     <row r="14">
@@ -6864,13 +6864,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10.75504610002381</v>
+        <v>10.44775906859456</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>291.6153928263598</v>
+        <v>300.5267167378081</v>
       </c>
     </row>
     <row r="15">
@@ -6878,13 +6878,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>16.84188186635403</v>
       </c>
       <c r="D15" t="n">
-        <v>295.6287774413208</v>
+        <v>301.7205219461722</v>
       </c>
     </row>
     <row r="16">
@@ -6892,13 +6892,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12.81278928812512</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>274.0283644524824</v>
+        <v>298.8273114617569</v>
       </c>
     </row>
     <row r="17">
@@ -6906,13 +6906,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13.69439872653876</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="C17" t="n">
-        <v>24.55547357862122</v>
+        <v>22.19437034990765</v>
       </c>
       <c r="D17" t="n">
-        <v>232.3325577054162</v>
+        <v>262.55467903295</v>
       </c>
     </row>
     <row r="18">
@@ -6920,13 +6920,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>14.98146996680633</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="C18" t="n">
-        <v>27.82272993835461</v>
+        <v>25.14746744428205</v>
       </c>
       <c r="D18" t="n">
-        <v>191.5487945755952</v>
+        <v>232.212784485498</v>
       </c>
     </row>
     <row r="19">
@@ -6934,13 +6934,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>15.04528356758237</v>
+        <v>14.44347222487907</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>28.28513310705485</v>
       </c>
       <c r="D19" t="n">
-        <v>122.7695139114721</v>
+        <v>188.3669502661313</v>
       </c>
     </row>
     <row r="20">
@@ -6948,13 +6948,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>12.77744637077223</v>
+        <v>15.46743508040849</v>
       </c>
       <c r="C20" t="n">
-        <v>36.31484758008951</v>
+        <v>31.60736733822606</v>
       </c>
       <c r="D20" t="n">
-        <v>41.02232782195296</v>
+        <v>129.1194580625405</v>
       </c>
     </row>
     <row r="21">
@@ -6962,13 +6962,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>25.33210706958902</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>56.99724090657529</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>18.99908030219176</v>
       </c>
     </row>
   </sheetData>
@@ -7007,13 +7007,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.169662426385451</v>
+        <v>2.507383636646354</v>
       </c>
       <c r="C2" t="n">
-        <v>6.077018289287756</v>
+        <v>6.907576847080557</v>
       </c>
       <c r="D2" t="n">
-        <v>100.879485349881</v>
+        <v>96.88180869818798</v>
       </c>
     </row>
     <row r="3">
@@ -7021,13 +7021,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.89878217547134</v>
+        <v>11.79569866652543</v>
       </c>
       <c r="C3" t="n">
-        <v>16.1890196430299</v>
+        <v>16.58171872472863</v>
       </c>
       <c r="D3" t="n">
-        <v>100.4524250985336</v>
+        <v>97.05557804183968</v>
       </c>
     </row>
     <row r="4">
@@ -7035,13 +7035,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.77396134831176</v>
+        <v>17.81675733667112</v>
       </c>
       <c r="C4" t="n">
-        <v>5.181664383014665</v>
+        <v>5.041274461307371</v>
       </c>
       <c r="D4" t="n">
-        <v>149.5535547787336</v>
+        <v>146.1076203368273</v>
       </c>
     </row>
     <row r="5">
@@ -7049,13 +7049,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2.380738182798515</v>
+        <v>2.159844949342983</v>
       </c>
       <c r="C5" t="n">
-        <v>4.66330159517235</v>
+        <v>4.540583132141498</v>
       </c>
       <c r="D5" t="n">
-        <v>113.0237044514141</v>
+        <v>118.3987731321654</v>
       </c>
     </row>
     <row r="6">
@@ -7063,13 +7063,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4.387430490278996</v>
+        <v>4.025165587411924</v>
       </c>
       <c r="C6" t="n">
-        <v>6.239006660488481</v>
+        <v>6.037748381117884</v>
       </c>
       <c r="D6" t="n">
-        <v>109.2027423864855</v>
+        <v>111.2958284919397</v>
       </c>
     </row>
     <row r="7">
@@ -7077,13 +7077,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.988660995905543</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="C7" t="n">
-        <v>7.485826244881928</v>
+        <v>7.186393195086651</v>
       </c>
       <c r="D7" t="n">
-        <v>149.2374320179661</v>
+        <v>141.2725128934118</v>
       </c>
     </row>
     <row r="8">
@@ -7091,13 +7091,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.593818492349078</v>
+        <v>7.176575718044183</v>
       </c>
       <c r="C8" t="n">
-        <v>9.346238144429634</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="D8" t="n">
-        <v>196.4378981427443</v>
+        <v>181.4171582677681</v>
       </c>
     </row>
     <row r="9">
@@ -7105,13 +7105,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.653124265231384</v>
+        <v>8.542186774651494</v>
       </c>
       <c r="C9" t="n">
-        <v>11.20468654856884</v>
+        <v>10.53906160508951</v>
       </c>
       <c r="D9" t="n">
-        <v>222.2077936315187</v>
+        <v>216.6609191025243</v>
       </c>
     </row>
     <row r="10">
@@ -7119,13 +7119,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>12.81180754042088</v>
+        <v>12.24239387195773</v>
       </c>
       <c r="D10" t="n">
-        <v>251.6808414607123</v>
+        <v>246.2714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -7136,10 +7136,10 @@
         <v>10.12869106471434</v>
       </c>
       <c r="C11" t="n">
-        <v>13.86031408855647</v>
+        <v>13.32722508515045</v>
       </c>
       <c r="D11" t="n">
-        <v>277.383978105598</v>
+        <v>274.3631404196306</v>
       </c>
     </row>
     <row r="12">
@@ -7147,13 +7147,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10.41437964665016</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="C12" t="n">
-        <v>14.75370449942107</v>
+        <v>14.53673825678252</v>
       </c>
       <c r="D12" t="n">
-        <v>284.8766765844097</v>
+        <v>290.5177988930119</v>
       </c>
     </row>
     <row r="13">
@@ -7161,13 +7161,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="C13" t="n">
-        <v>14.30897278939726</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>292.423371186955</v>
+        <v>298.9274497275901</v>
       </c>
     </row>
     <row r="14">
@@ -7175,13 +7175,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10.44775906859456</v>
+        <v>10.14047203716531</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>289.4643836063551</v>
+        <v>298.6829945492327</v>
       </c>
     </row>
     <row r="15">
@@ -7189,13 +7189,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>11.46681318560274</v>
+        <v>10.75013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>16.48354395430394</v>
       </c>
       <c r="D15" t="n">
-        <v>287.3870054641688</v>
+        <v>299.2121565618216</v>
       </c>
     </row>
     <row r="16">
@@ -7203,13 +7203,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12.39947350463721</v>
+        <v>11.5728419376614</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>259.5623120304057</v>
+        <v>296.3474167608294</v>
       </c>
     </row>
     <row r="17">
@@ -7217,13 +7217,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13.22217808079604</v>
+        <v>12.27773678931061</v>
       </c>
       <c r="C17" t="n">
-        <v>25.02769422436394</v>
+        <v>21.72214970416493</v>
       </c>
       <c r="D17" t="n">
-        <v>216.7492763959066</v>
+        <v>265.860223553149</v>
       </c>
     </row>
     <row r="18">
@@ -7231,13 +7231,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13.9113649691773</v>
+        <v>12.84125997154828</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>24.61241494546753</v>
       </c>
       <c r="D18" t="n">
-        <v>166.9363796301276</v>
+        <v>231.6777319866836</v>
       </c>
     </row>
     <row r="19">
@@ -7245,13 +7245,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12.63803819676919</v>
+        <v>13.23984953947248</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>27.68332176435156</v>
       </c>
       <c r="D19" t="n">
-        <v>90.27170140549421</v>
+        <v>189.5705729515379</v>
       </c>
     </row>
     <row r="20">
@@ -7259,13 +7259,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>23.53740120931727</v>
+        <v>30.93487016081699</v>
       </c>
       <c r="D20" t="n">
-        <v>23.53740120931727</v>
+        <v>131.8094467721767</v>
       </c>
     </row>
     <row r="21">
@@ -7273,13 +7273,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>27.71814676871718</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>66.84964808925908</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>29.34862599040643</v>
       </c>
     </row>
   </sheetData>
@@ -7318,13 +7318,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3652101459798134</v>
+        <v>2.189297380470387</v>
       </c>
       <c r="C2" t="n">
-        <v>10.95335913628166</v>
+        <v>12.00775617064274</v>
       </c>
       <c r="D2" t="n">
-        <v>167.9966671507142</v>
+        <v>160.3881224428014</v>
       </c>
     </row>
     <row r="3">
@@ -7332,13 +7332,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.665306148309849</v>
+        <v>10.14145378486955</v>
       </c>
       <c r="C3" t="n">
-        <v>18.95754816900591</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D3" t="n">
-        <v>127.1412364384832</v>
+        <v>122.6055620448629</v>
       </c>
     </row>
     <row r="4">
@@ -7346,13 +7346,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.40758952817845</v>
+        <v>19.00369031110551</v>
       </c>
       <c r="C4" t="n">
-        <v>18.93987671032947</v>
+        <v>17.62531653434299</v>
       </c>
       <c r="D4" t="n">
-        <v>157.1473732710827</v>
+        <v>150.4597079097534</v>
       </c>
     </row>
     <row r="5">
@@ -7360,13 +7360,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.24730261047896</v>
+        <v>11.51099183229385</v>
       </c>
       <c r="C5" t="n">
-        <v>6.43044746281661</v>
+        <v>6.111379458936396</v>
       </c>
       <c r="D5" t="n">
-        <v>122.9884436495192</v>
+        <v>130.4006388165826</v>
       </c>
     </row>
     <row r="6">
@@ -7374,13 +7374,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4.065417243286043</v>
+        <v>3.542145716922492</v>
       </c>
       <c r="C6" t="n">
-        <v>6.681774875103793</v>
+        <v>6.31950997223672</v>
       </c>
       <c r="D6" t="n">
-        <v>114.113444403128</v>
+        <v>116.0052722292116</v>
       </c>
     </row>
     <row r="7">
@@ -7388,13 +7388,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.868887775987432</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="C7" t="n">
-        <v>8.024805734513427</v>
+        <v>7.665486074759095</v>
       </c>
       <c r="D7" t="n">
-        <v>149.7764115075976</v>
+        <v>140.5538735739031</v>
       </c>
     </row>
     <row r="8">
@@ -7402,13 +7402,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.42692138262712</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>9.680032363873551</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="D8" t="n">
-        <v>199.9427374469054</v>
+        <v>179.0805987316607</v>
       </c>
     </row>
     <row r="9">
@@ -7416,13 +7416,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.542186774651494</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="C9" t="n">
-        <v>11.6484365108884</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="D9" t="n">
-        <v>223.6499810090573</v>
+        <v>214.4421692909265</v>
       </c>
     </row>
     <row r="10">
@@ -7430,13 +7430,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>9.110618695410402</v>
       </c>
       <c r="C10" t="n">
-        <v>13.23886779176824</v>
+        <v>12.38474728907351</v>
       </c>
       <c r="D10" t="n">
-        <v>251.9655482949439</v>
+        <v>244.1361103535756</v>
       </c>
     </row>
     <row r="11">
@@ -7444,13 +7444,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.950994730245668</v>
+        <v>9.773298395776996</v>
       </c>
       <c r="C11" t="n">
-        <v>14.39340309196248</v>
+        <v>13.68261775408779</v>
       </c>
       <c r="D11" t="n">
-        <v>275.6070147609113</v>
+        <v>274.3631404196306</v>
       </c>
     </row>
     <row r="12">
@@ -7458,13 +7458,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10.41437964665016</v>
+        <v>9.980447161373073</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>14.75370449942107</v>
       </c>
       <c r="D12" t="n">
-        <v>282.2730816727471</v>
+        <v>288.1311702239879</v>
       </c>
     </row>
     <row r="13">
@@ -7472,13 +7472,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>287.7404346376977</v>
+        <v>296.5859814529614</v>
       </c>
     </row>
     <row r="14">
@@ -7486,13 +7486,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10.14047203716531</v>
+        <v>9.525897974306801</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>286.3915132920625</v>
+        <v>296.8392723606571</v>
       </c>
     </row>
     <row r="15">
@@ -7500,13 +7500,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10.75013736150257</v>
+        <v>10.0334615374024</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>278.0702197508666</v>
+        <v>297.0621290895211</v>
       </c>
     </row>
     <row r="16">
@@ -7514,13 +7514,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11.98615772114931</v>
+        <v>10.74621037068559</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>245.0962596083289</v>
+        <v>293.8675220599019</v>
       </c>
     </row>
     <row r="17">
@@ -7528,13 +7528,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12.74995743505333</v>
+        <v>11.33329549782518</v>
       </c>
       <c r="C17" t="n">
-        <v>25.97213551584937</v>
+        <v>21.24992905842221</v>
       </c>
       <c r="D17" t="n">
-        <v>198.8048918576833</v>
+        <v>268.6935474276053</v>
       </c>
     </row>
     <row r="18">
@@ -7542,13 +7542,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12.30620747273377</v>
+        <v>11.77115497391926</v>
       </c>
       <c r="C18" t="n">
-        <v>31.56809743005619</v>
+        <v>24.07736244665303</v>
       </c>
       <c r="D18" t="n">
-        <v>140.1837546894021</v>
+        <v>231.6777319866836</v>
       </c>
     </row>
     <row r="19">
@@ -7556,13 +7556,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>8.425358797846126</v>
+        <v>12.03622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>32.49781250597791</v>
+        <v>27.08151042164826</v>
       </c>
       <c r="D19" t="n">
-        <v>63.79200232654924</v>
+        <v>190.1723842942411</v>
       </c>
     </row>
     <row r="20">
@@ -7570,13 +7570,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.017491532227195</v>
+        <v>12.77744637077223</v>
       </c>
       <c r="C20" t="n">
-        <v>15.46743508040849</v>
+        <v>30.26237298340792</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>134.499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -7584,13 +7584,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>30.20087226082804</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>77.18000688878276</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>40.26782968110405</v>
       </c>
     </row>
   </sheetData>
@@ -7629,13 +7629,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.186352137357647</v>
+        <v>4.286310476741575</v>
       </c>
       <c r="C2" t="n">
-        <v>8.032659716147403</v>
+        <v>9.173450548482196</v>
       </c>
       <c r="D2" t="n">
-        <v>161.1931555602838</v>
+        <v>154.682204785719</v>
       </c>
     </row>
     <row r="3">
@@ -7643,13 +7643,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4.540583132141498</v>
+        <v>7.328746612202441</v>
       </c>
       <c r="C3" t="n">
-        <v>26.51700549170635</v>
+        <v>27.15023276094554</v>
       </c>
       <c r="D3" t="n">
-        <v>167.1229116939345</v>
+        <v>155.2732169036755</v>
       </c>
     </row>
     <row r="4">
@@ -7657,13 +7657,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.59229696529709</v>
+        <v>12.81377103582937</v>
       </c>
       <c r="C4" t="n">
-        <v>24.65757533986289</v>
+        <v>23.63655772744621</v>
       </c>
       <c r="D4" t="n">
-        <v>147.3966550725034</v>
+        <v>137.275817989423</v>
       </c>
     </row>
     <row r="5">
@@ -7671,13 +7671,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.07549676223577</v>
+        <v>10.97103059495811</v>
       </c>
       <c r="C5" t="n">
-        <v>12.68908907739003</v>
+        <v>11.36372967665683</v>
       </c>
       <c r="D5" t="n">
-        <v>108.2376843932109</v>
+        <v>113.0727918366264</v>
       </c>
     </row>
     <row r="6">
@@ -7685,13 +7685,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4.830198704894308</v>
+        <v>4.588688769649592</v>
       </c>
       <c r="C6" t="n">
-        <v>5.474225198880216</v>
+        <v>5.031456984264904</v>
       </c>
       <c r="D6" t="n">
-        <v>93.5448482514531</v>
+        <v>95.31592110991434</v>
       </c>
     </row>
     <row r="7">
@@ -7699,13 +7699,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.87455727803466</v>
+        <v>2.455351008321272</v>
       </c>
       <c r="C7" t="n">
-        <v>5.689227946110266</v>
+        <v>5.329908286355933</v>
       </c>
       <c r="D7" t="n">
-        <v>113.8444455321644</v>
+        <v>106.3586192872825</v>
       </c>
     </row>
     <row r="8">
@@ -7713,13 +7713,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.504839304161113</v>
+        <v>3.171045084717197</v>
       </c>
       <c r="C8" t="n">
-        <v>6.425538724295373</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="D8" t="n">
-        <v>151.3756785178157</v>
+        <v>130.6804369122929</v>
       </c>
     </row>
     <row r="9">
@@ -7727,13 +7727,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.882812170296134</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>7.432811868852599</v>
+        <v>6.767186925373262</v>
       </c>
       <c r="D9" t="n">
-        <v>160.7484238502599</v>
+        <v>155.3124868118453</v>
       </c>
     </row>
     <row r="10">
@@ -7741,13 +7741,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>8.256498192715677</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="D10" t="n">
-        <v>179.5076589830081</v>
+        <v>172.3899881272187</v>
       </c>
     </row>
     <row r="11">
@@ -7755,13 +7755,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="D11" t="n">
-        <v>192.4451302295725</v>
+        <v>191.0235595538231</v>
       </c>
     </row>
     <row r="12">
@@ -7769,13 +7769,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>9.112582190818895</v>
+        <v>8.678649705541803</v>
       </c>
       <c r="D12" t="n">
-        <v>194.4017534041364</v>
+        <v>199.1750107421844</v>
       </c>
     </row>
     <row r="13">
@@ -7783,13 +7783,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.642283982755667</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>8.585383673638358</v>
+        <v>8.845546815263763</v>
       </c>
       <c r="D13" t="n">
-        <v>195.1223562190536</v>
+        <v>203.1874136094411</v>
       </c>
     </row>
     <row r="14">
@@ -7797,13 +7797,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3.994731408580272</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>10.44775906859456</v>
+        <v>8.911323911448299</v>
       </c>
       <c r="D14" t="n">
-        <v>192.97625573757</v>
+        <v>201.8875796490184</v>
       </c>
     </row>
     <row r="15">
@@ -7811,13 +7811,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3.941717032550943</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>10.75013736150257</v>
+        <v>8.958447801252145</v>
       </c>
       <c r="D15" t="n">
-        <v>181.6773214093935</v>
+        <v>202.4609203082985</v>
       </c>
     </row>
     <row r="16">
@@ -7825,13 +7825,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>9.919578803709772</v>
       </c>
       <c r="D16" t="n">
-        <v>155.4067345914531</v>
+        <v>196.7383129402438</v>
       </c>
     </row>
     <row r="17">
@@ -7839,13 +7839,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>11.33329549782518</v>
       </c>
       <c r="D17" t="n">
-        <v>119.9440440186498</v>
+        <v>179.9160660279747</v>
       </c>
     </row>
     <row r="18">
@@ -7853,13 +7853,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.745367491701582</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>12.84125997154828</v>
       </c>
       <c r="D18" t="n">
-        <v>75.97745483166067</v>
+        <v>155.1652246562084</v>
       </c>
     </row>
     <row r="19">
@@ -7867,13 +7867,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.805434028109884</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>15.04528356758237</v>
+        <v>14.44347222487907</v>
       </c>
       <c r="D19" t="n">
-        <v>28.88694444975815</v>
+        <v>126.9821933103952</v>
       </c>
     </row>
     <row r="20">
@@ -7881,13 +7881,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>5.37997741927252</v>
+        <v>16.13993225781756</v>
       </c>
       <c r="D20" t="n">
-        <v>4.707480241863455</v>
+        <v>90.78711895022377</v>
       </c>
     </row>
     <row r="21">
@@ -7895,13 +7895,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>12.06950545928009</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>46.55380677150892</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>34.48430131222884</v>
       </c>
     </row>
   </sheetData>
@@ -7943,10 +7943,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>7.089200172366218</v>
+        <v>8.04542243630261</v>
       </c>
       <c r="D2" t="n">
-        <v>173.234291152871</v>
+        <v>169.2120708085717</v>
       </c>
     </row>
     <row r="3">
@@ -7954,13 +7954,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6.391177554646736</v>
+        <v>11.36372967665683</v>
       </c>
       <c r="C3" t="n">
-        <v>29.11372816943916</v>
+        <v>31.05758862384785</v>
       </c>
       <c r="D3" t="n">
-        <v>229.8467725182633</v>
+        <v>210.1185524014236</v>
       </c>
     </row>
     <row r="4">
@@ -7968,13 +7968,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.28224461720434</v>
+        <v>13.51572064436584</v>
       </c>
       <c r="C4" t="n">
-        <v>45.62672455487051</v>
+        <v>44.09519813624549</v>
       </c>
       <c r="D4" t="n">
-        <v>180.1585577109237</v>
+        <v>165.0347343270016</v>
       </c>
     </row>
     <row r="5">
@@ -7982,13 +7982,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16.5915362017711</v>
+        <v>15.21708941582556</v>
       </c>
       <c r="C5" t="n">
-        <v>28.20070280448963</v>
+        <v>25.94268308472197</v>
       </c>
       <c r="D5" t="n">
-        <v>123.4302301164303</v>
+        <v>128.4616871006952</v>
       </c>
     </row>
     <row r="6">
@@ -7996,13 +7996,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.58618549489336</v>
+        <v>9.781152377410974</v>
       </c>
       <c r="C6" t="n">
-        <v>11.95474179461341</v>
+        <v>10.90819874188631</v>
       </c>
       <c r="D6" t="n">
-        <v>101.3536694910322</v>
+        <v>103.5272589082347</v>
       </c>
     </row>
     <row r="7">
@@ -8010,13 +8010,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.311835917051991</v>
+        <v>4.07228947721577</v>
       </c>
       <c r="C7" t="n">
-        <v>6.767186925373263</v>
+        <v>6.168320825782709</v>
       </c>
       <c r="D7" t="n">
-        <v>116.8986626400762</v>
+        <v>108.3947640258903</v>
       </c>
     </row>
     <row r="8">
@@ -8024,13 +8024,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.504839304161113</v>
+        <v>3.00414797499524</v>
       </c>
       <c r="C8" t="n">
-        <v>7.093127163183205</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="D8" t="n">
-        <v>151.6260241823986</v>
+        <v>130.0962970282661</v>
       </c>
     </row>
     <row r="9">
@@ -8038,13 +8038,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.882812170296134</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>7.876561831172157</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="D9" t="n">
-        <v>164.5202985299762</v>
+        <v>154.3140493966264</v>
       </c>
     </row>
     <row r="10">
@@ -8052,13 +8052,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>8.683558444063038</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="D10" t="n">
-        <v>181.9276670739764</v>
+        <v>173.6711688812608</v>
       </c>
     </row>
     <row r="11">
@@ -8066,13 +8066,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>9.240209392370978</v>
+        <v>8.529424054496287</v>
       </c>
       <c r="D11" t="n">
-        <v>191.5566485572291</v>
+        <v>189.7796852125424</v>
       </c>
     </row>
     <row r="12">
@@ -8080,13 +8080,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>9.546514676095983</v>
+        <v>8.895615948180348</v>
       </c>
       <c r="D12" t="n">
-        <v>192.666023463028</v>
+        <v>198.7410782569073</v>
       </c>
     </row>
     <row r="13">
@@ -8094,13 +8094,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.642283982755667</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>194.081703652552</v>
+        <v>202.9272504678157</v>
       </c>
     </row>
     <row r="14">
@@ -8111,10 +8111,10 @@
         <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>10.44775906859456</v>
+        <v>9.21861094287755</v>
       </c>
       <c r="D14" t="n">
-        <v>188.059663234702</v>
+        <v>203.7313018375938</v>
       </c>
     </row>
     <row r="15">
@@ -8122,13 +8122,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3.583379120500858</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>11.46681318560274</v>
+        <v>9.316785713302231</v>
       </c>
       <c r="D15" t="n">
-        <v>174.8689010804418</v>
+        <v>201.3859065721482</v>
       </c>
     </row>
     <row r="16">
@@ -8136,13 +8136,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.133157834879071</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>9.506263020221864</v>
       </c>
       <c r="D16" t="n">
-        <v>145.4871557877433</v>
+        <v>196.3249971567559</v>
       </c>
     </row>
     <row r="17">
@@ -8150,13 +8150,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.249985811684442</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>10.86107485208246</v>
       </c>
       <c r="D17" t="n">
-        <v>107.1940865835965</v>
+        <v>180.3882866737175</v>
       </c>
     </row>
     <row r="18">
@@ -8164,13 +8164,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>12.30620747273377</v>
       </c>
       <c r="D18" t="n">
-        <v>59.92587986722531</v>
+        <v>156.7703821526519</v>
       </c>
     </row>
     <row r="19">
@@ -8178,13 +8178,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>12.63803819676919</v>
+        <v>13.84166088217578</v>
       </c>
       <c r="D19" t="n">
-        <v>19.85977430920873</v>
+        <v>129.9912500239116</v>
       </c>
     </row>
     <row r="20">
@@ -8192,13 +8192,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>3.362485887045325</v>
+        <v>15.46743508040849</v>
       </c>
       <c r="D20" t="n">
-        <v>2.68998870963626</v>
+        <v>93.47710765986002</v>
       </c>
     </row>
     <row r="21">
@@ -8206,13 +8206,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>12.54213327820564</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>54.64786642646742</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>45.68919979917768</v>
       </c>
     </row>
   </sheetData>
@@ -8254,10 +8254,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>3.799363615435156</v>
+        <v>4.633849164044945</v>
       </c>
       <c r="D2" t="n">
-        <v>133.0523393657532</v>
+        <v>129.9627793404885</v>
       </c>
     </row>
     <row r="3">
@@ -8265,13 +8265,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.255115534383929</v>
+        <v>11.89387343695011</v>
       </c>
       <c r="C3" t="n">
-        <v>36.19212911705866</v>
+        <v>38.93120521190727</v>
       </c>
       <c r="D3" t="n">
-        <v>259.0095880729147</v>
+        <v>238.5352397008475</v>
       </c>
     </row>
     <row r="4">
@@ -8279,13 +8279,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.8648219164502</v>
+        <v>13.06902543893354</v>
       </c>
       <c r="C4" t="n">
-        <v>54.15222161854981</v>
+        <v>48.77911643320702</v>
       </c>
       <c r="D4" t="n">
-        <v>171.1480772813465</v>
+        <v>158.7299505703286</v>
       </c>
     </row>
     <row r="5">
@@ -8293,13 +8293,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>5.964117303299374</v>
+        <v>5.497787143782139</v>
       </c>
       <c r="C5" t="n">
-        <v>19.85584731839174</v>
+        <v>18.45685683984004</v>
       </c>
       <c r="D5" t="n">
-        <v>115.9444038715483</v>
+        <v>119.7486762255047</v>
       </c>
     </row>
     <row r="6">
@@ -8307,13 +8307,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.656609287691869</v>
+        <v>2.495602664195392</v>
       </c>
       <c r="C6" t="n">
-        <v>4.427682146153116</v>
+        <v>4.025165587411924</v>
       </c>
       <c r="D6" t="n">
-        <v>98.81781517096272</v>
+        <v>97.77127211823561</v>
       </c>
     </row>
     <row r="7">
@@ -8321,13 +8321,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.275691178444106</v>
+        <v>1.976258128648829</v>
       </c>
       <c r="C7" t="n">
-        <v>4.970588626601601</v>
+        <v>4.551382356888213</v>
       </c>
       <c r="D7" t="n">
-        <v>106.5981657271187</v>
+        <v>91.44685340747763</v>
       </c>
     </row>
     <row r="8">
@@ -8335,13 +8335,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.670353755551324</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>5.757950285407543</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="D8" t="n">
-        <v>121.2507502130023</v>
+        <v>113.7403802755142</v>
       </c>
     </row>
     <row r="9">
@@ -8349,13 +8349,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.995312245657018</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>6.545311944213482</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="D9" t="n">
-        <v>138.8937382060217</v>
+        <v>132.570301242968</v>
       </c>
     </row>
     <row r="10">
@@ -8363,13 +8363,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.131775176547325</v>
+        <v>2.989421759431538</v>
       </c>
       <c r="C10" t="n">
-        <v>7.117670855789377</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="D10" t="n">
-        <v>150.3252084742716</v>
+        <v>148.9016743031137</v>
       </c>
     </row>
     <row r="11">
@@ -8377,13 +8377,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="D11" t="n">
-        <v>154.5958109877452</v>
+        <v>159.3936120183994</v>
       </c>
     </row>
     <row r="12">
@@ -8391,13 +8391,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.603594911662541</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="D12" t="n">
-        <v>158.6023233687765</v>
+        <v>165.7622093758484</v>
       </c>
     </row>
     <row r="13">
@@ -8408,10 +8408,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>8.585383673638358</v>
+        <v>7.544731107136739</v>
       </c>
       <c r="D13" t="n">
-        <v>155.8377218336175</v>
+        <v>168.8458789148877</v>
       </c>
     </row>
     <row r="14">
@@ -8419,13 +8419,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.765583282863265</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>9.525897974306801</v>
+        <v>7.682175785731292</v>
       </c>
       <c r="D14" t="n">
-        <v>146.8832010231823</v>
+        <v>169.0078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -8433,13 +8433,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3.225041208450772</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>10.75013736150257</v>
+        <v>7.883434065101886</v>
       </c>
       <c r="D15" t="n">
-        <v>123.2682417452295</v>
+        <v>166.6271291032899</v>
       </c>
     </row>
     <row r="16">
@@ -8447,13 +8447,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>9.092947236733956</v>
       </c>
       <c r="D16" t="n">
-        <v>91.75610393431539</v>
+        <v>154.5801030244773</v>
       </c>
     </row>
     <row r="17">
@@ -8461,13 +8461,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.888882582970863</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>10.38885420633975</v>
       </c>
       <c r="D17" t="n">
-        <v>51.47205038595602</v>
+        <v>135.5273253281594</v>
       </c>
     </row>
     <row r="18">
@@ -8475,13 +8475,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>2.675262494072558</v>
       </c>
       <c r="C18" t="n">
-        <v>10.70104997629023</v>
+        <v>11.77115497391926</v>
       </c>
       <c r="D18" t="n">
-        <v>17.12167996206437</v>
+        <v>112.896077249862</v>
       </c>
     </row>
     <row r="19">
@@ -8489,13 +8489,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>2.407245370813179</v>
+        <v>13.23984953947248</v>
       </c>
       <c r="D19" t="n">
-        <v>1.805434028109884</v>
+        <v>81.84634260764808</v>
       </c>
     </row>
     <row r="20">
@@ -8503,13 +8503,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>8.06996612890878</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>32.95236169304418</v>
       </c>
     </row>
     <row r="21">
@@ -8565,10 +8565,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1.721985473248905</v>
+        <v>2.1853703896534</v>
       </c>
       <c r="D2" t="n">
-        <v>99.35973990370694</v>
+        <v>98.40744463058752</v>
       </c>
     </row>
     <row r="3">
@@ -8576,13 +8576,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3.396847056693964</v>
+        <v>5.973934780341842</v>
       </c>
       <c r="C3" t="n">
-        <v>25.57452769562941</v>
+        <v>29.07445826126929</v>
       </c>
       <c r="D3" t="n">
-        <v>293.3167615978195</v>
+        <v>269.0921369955295</v>
       </c>
     </row>
     <row r="4">
@@ -8590,13 +8590,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.57502641724815</v>
+        <v>18.25068982194821</v>
       </c>
       <c r="C4" t="n">
-        <v>74.78954010952202</v>
+        <v>72.8240812056199</v>
       </c>
       <c r="D4" t="n">
-        <v>228.7334706216474</v>
+        <v>210.0998991950429</v>
       </c>
     </row>
     <row r="5">
@@ -8604,13 +8604,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.41281706186917</v>
+        <v>11.02011798017045</v>
       </c>
       <c r="C5" t="n">
-        <v>55.37057051952011</v>
+        <v>49.16101629015904</v>
       </c>
       <c r="D5" t="n">
-        <v>133.2231634662922</v>
+        <v>134.4258044039945</v>
       </c>
     </row>
     <row r="6">
@@ -8618,13 +8618,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4.266675522656639</v>
+        <v>3.944662275663684</v>
       </c>
       <c r="C6" t="n">
-        <v>14.20883452356409</v>
+        <v>13.28304643845935</v>
       </c>
       <c r="D6" t="n">
-        <v>106.5058814429195</v>
+        <v>104.8555635520806</v>
       </c>
     </row>
     <row r="7">
@@ -8632,13 +8632,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.515237618280328</v>
+        <v>2.395464398362217</v>
       </c>
       <c r="C7" t="n">
-        <v>5.868887775987432</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="D7" t="n">
-        <v>110.1314757147029</v>
+        <v>97.79483406313751</v>
       </c>
     </row>
     <row r="8">
@@ -8646,13 +8646,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.00414797499524</v>
+        <v>2.586905200690345</v>
       </c>
       <c r="C8" t="n">
-        <v>7.176575718044183</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="D8" t="n">
-        <v>126.7583548338269</v>
+        <v>118.413499347729</v>
       </c>
     </row>
     <row r="9">
@@ -8663,10 +8663,10 @@
         <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>7.432811868852599</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="D9" t="n">
-        <v>145.8828001125547</v>
+        <v>139.0046756966016</v>
       </c>
     </row>
     <row r="10">
@@ -8674,13 +8674,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.2776546738526</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>8.256498192715677</v>
+        <v>7.687084524252525</v>
       </c>
       <c r="D10" t="n">
-        <v>157.0158190787136</v>
+        <v>157.1581724958294</v>
       </c>
     </row>
     <row r="11">
@@ -8688,13 +8688,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.954659679155399</v>
+        <v>2.132356013624072</v>
       </c>
       <c r="C11" t="n">
-        <v>7.996335051090269</v>
+        <v>8.529424054496287</v>
       </c>
       <c r="D11" t="n">
-        <v>165.2575910558655</v>
+        <v>171.4769627622691</v>
       </c>
     </row>
     <row r="12">
@@ -8705,10 +8705,10 @@
         <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>6.942919764433443</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="D12" t="n">
-        <v>167.7149055595953</v>
+        <v>182.0346775737393</v>
       </c>
     </row>
     <row r="13">
@@ -8716,13 +8716,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>7.804894248762142</v>
+        <v>6.243915399009714</v>
       </c>
       <c r="D13" t="n">
-        <v>121.7563502806894</v>
+        <v>174.829631172272</v>
       </c>
     </row>
     <row r="14">
@@ -8730,13 +8730,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.458296251434013</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>8.911323911448299</v>
+        <v>6.453027660014286</v>
       </c>
       <c r="D14" t="n">
-        <v>103.5557295916578</v>
+        <v>139.8155993003095</v>
       </c>
     </row>
     <row r="15">
@@ -8744,13 +8744,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>10.75013736150257</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="D15" t="n">
-        <v>77.75932691486861</v>
+        <v>131.1516758103314</v>
       </c>
     </row>
     <row r="16">
@@ -8758,13 +8758,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>8.679631453246051</v>
       </c>
       <c r="D16" t="n">
-        <v>43.81147304971816</v>
+        <v>116.1417351601019</v>
       </c>
     </row>
     <row r="17">
@@ -8772,13 +8772,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1.888882582970863</v>
       </c>
       <c r="C17" t="n">
-        <v>8.9721922691116</v>
+        <v>9.916633560597033</v>
       </c>
       <c r="D17" t="n">
-        <v>14.63884001802419</v>
+        <v>97.27745302299945</v>
       </c>
     </row>
     <row r="18">
@@ -8786,13 +8786,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>1.605157496443535</v>
+        <v>11.23610247510475</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>71.16198234233005</v>
       </c>
     </row>
     <row r="19">
@@ -8800,13 +8800,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>6.619924769736241</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>28.88694444975815</v>
       </c>
     </row>
     <row r="20">
